--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/sensitivity/D7_track_invariance.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/sensitivity/D7_track_invariance.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0408311328842481</v>
+        <v>0.03935563516067416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8444773079906904</v>
+        <v>0.8507773526420304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9782489353461186</v>
+        <v>0.9784114134856962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00795609457998403</v>
+        <v>0.01201052977953271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>e42f5c5c7cc85daf6f1d5675fc5b5e0f9d9e22003444d6fa284ed31a9823ba76</t>
+          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>e42f5c5c7cc85daf6f1d5675fc5b5e0f9d9e22003444d6fa284ed31a9823ba76</t>
+          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
         </is>
       </c>
     </row>
@@ -676,14 +676,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>e42f5c5c7cc85daf6f1d5675fc5b5e0f9d9e22003444d6fa284ed31a9823ba76</t>
+          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
         </is>
       </c>
     </row>
@@ -712,14 +712,14 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>e42f5c5c7cc85daf6f1d5675fc5b5e0f9d9e22003444d6fa284ed31a9823ba76</t>
+          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
         </is>
       </c>
     </row>
@@ -748,14 +748,14 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>e42f5c5c7cc85daf6f1d5675fc5b5e0f9d9e22003444d6fa284ed31a9823ba76</t>
+          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
         </is>
       </c>
     </row>
@@ -784,14 +784,14 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>e42f5c5c7cc85daf6f1d5675fc5b5e0f9d9e22003444d6fa284ed31a9823ba76</t>
+          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
         </is>
       </c>
     </row>
@@ -820,14 +820,14 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>e42f5c5c7cc85daf6f1d5675fc5b5e0f9d9e22003444d6fa284ed31a9823ba76</t>
+          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
         </is>
       </c>
     </row>
@@ -856,14 +856,14 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>e42f5c5c7cc85daf6f1d5675fc5b5e0f9d9e22003444d6fa284ed31a9823ba76</t>
+          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
         </is>
       </c>
     </row>
@@ -892,14 +892,14 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7c54c2df1ab5e5b5ca2f9e355d993211e5e2029c84c5388c8efd03b16e804fb8</t>
+          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
         </is>
       </c>
     </row>
@@ -928,14 +928,14 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7c54c2df1ab5e5b5ca2f9e355d993211e5e2029c84c5388c8efd03b16e804fb8</t>
+          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
         </is>
       </c>
     </row>
@@ -964,14 +964,14 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7c54c2df1ab5e5b5ca2f9e355d993211e5e2029c84c5388c8efd03b16e804fb8</t>
+          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
         </is>
       </c>
     </row>
@@ -1000,14 +1000,14 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7c54c2df1ab5e5b5ca2f9e355d993211e5e2029c84c5388c8efd03b16e804fb8</t>
+          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7c54c2df1ab5e5b5ca2f9e355d993211e5e2029c84c5388c8efd03b16e804fb8</t>
+          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
         </is>
       </c>
     </row>
@@ -1072,14 +1072,14 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7c54c2df1ab5e5b5ca2f9e355d993211e5e2029c84c5388c8efd03b16e804fb8</t>
+          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
         </is>
       </c>
     </row>
@@ -1108,14 +1108,14 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7c54c2df1ab5e5b5ca2f9e355d993211e5e2029c84c5388c8efd03b16e804fb8</t>
+          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
         </is>
       </c>
     </row>
@@ -1144,14 +1144,14 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7c54c2df1ab5e5b5ca2f9e355d993211e5e2029c84c5388c8efd03b16e804fb8</t>
+          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
         </is>
       </c>
     </row>
@@ -1180,14 +1180,14 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>bef0a6b02a9d3c8ee3a214d5c30008a04423de13ea99db3d8525c8a9fdd51b62</t>
+          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>bef0a6b02a9d3c8ee3a214d5c30008a04423de13ea99db3d8525c8a9fdd51b62</t>
+          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
         </is>
       </c>
     </row>
@@ -1252,14 +1252,14 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>bef0a6b02a9d3c8ee3a214d5c30008a04423de13ea99db3d8525c8a9fdd51b62</t>
+          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
         </is>
       </c>
     </row>
@@ -1288,14 +1288,14 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>bef0a6b02a9d3c8ee3a214d5c30008a04423de13ea99db3d8525c8a9fdd51b62</t>
+          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1324,14 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>bef0a6b02a9d3c8ee3a214d5c30008a04423de13ea99db3d8525c8a9fdd51b62</t>
+          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
         </is>
       </c>
     </row>
@@ -1360,14 +1360,14 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>bef0a6b02a9d3c8ee3a214d5c30008a04423de13ea99db3d8525c8a9fdd51b62</t>
+          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
         </is>
       </c>
     </row>
@@ -1396,14 +1396,14 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>bef0a6b02a9d3c8ee3a214d5c30008a04423de13ea99db3d8525c8a9fdd51b62</t>
+          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>bef0a6b02a9d3c8ee3a214d5c30008a04423de13ea99db3d8525c8a9fdd51b62</t>
+          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
         </is>
       </c>
     </row>
@@ -1468,14 +1468,14 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G26" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>05b00f7dbd19991cb780da0a1098b2bc04983e4f98c6a28dfe2e9f5281a702a5</t>
+          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
         </is>
       </c>
     </row>
@@ -1504,14 +1504,14 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G27" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>05b00f7dbd19991cb780da0a1098b2bc04983e4f98c6a28dfe2e9f5281a702a5</t>
+          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
         </is>
       </c>
     </row>
@@ -1540,14 +1540,14 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G28" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>05b00f7dbd19991cb780da0a1098b2bc04983e4f98c6a28dfe2e9f5281a702a5</t>
+          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
         </is>
       </c>
     </row>
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G29" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>05b00f7dbd19991cb780da0a1098b2bc04983e4f98c6a28dfe2e9f5281a702a5</t>
+          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
         </is>
       </c>
     </row>
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G30" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>05b00f7dbd19991cb780da0a1098b2bc04983e4f98c6a28dfe2e9f5281a702a5</t>
+          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
         </is>
       </c>
     </row>
@@ -1648,14 +1648,14 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G31" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>05b00f7dbd19991cb780da0a1098b2bc04983e4f98c6a28dfe2e9f5281a702a5</t>
+          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
         </is>
       </c>
     </row>
@@ -1684,14 +1684,14 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G32" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>05b00f7dbd19991cb780da0a1098b2bc04983e4f98c6a28dfe2e9f5281a702a5</t>
+          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
         </is>
       </c>
     </row>
@@ -1720,14 +1720,14 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G33" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>05b00f7dbd19991cb780da0a1098b2bc04983e4f98c6a28dfe2e9f5281a702a5</t>
+          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
         </is>
       </c>
     </row>
@@ -1756,14 +1756,14 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>d578ba334583ada60c227a3bd3028700b7cc2108a79b2d6c58150bbd7f9dd37d</t>
+          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
         </is>
       </c>
     </row>
@@ -1792,14 +1792,14 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>d578ba334583ada60c227a3bd3028700b7cc2108a79b2d6c58150bbd7f9dd37d</t>
+          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>d578ba334583ada60c227a3bd3028700b7cc2108a79b2d6c58150bbd7f9dd37d</t>
+          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
         </is>
       </c>
     </row>
@@ -1864,14 +1864,14 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>d578ba334583ada60c227a3bd3028700b7cc2108a79b2d6c58150bbd7f9dd37d</t>
+          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
         </is>
       </c>
     </row>
@@ -1900,14 +1900,14 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>d578ba334583ada60c227a3bd3028700b7cc2108a79b2d6c58150bbd7f9dd37d</t>
+          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
         </is>
       </c>
     </row>
@@ -1936,14 +1936,14 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>d578ba334583ada60c227a3bd3028700b7cc2108a79b2d6c58150bbd7f9dd37d</t>
+          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
         </is>
       </c>
     </row>
@@ -1972,14 +1972,14 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>b70d64270865ffdb564b96de6937670c517bf091abeff4cca16ed4e76111c722</t>
+          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
         </is>
       </c>
     </row>
@@ -2008,14 +2008,14 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>b70d64270865ffdb564b96de6937670c517bf091abeff4cca16ed4e76111c722</t>
+          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
         </is>
       </c>
     </row>
@@ -2044,14 +2044,14 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>b70d64270865ffdb564b96de6937670c517bf091abeff4cca16ed4e76111c722</t>
+          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
         </is>
       </c>
     </row>
@@ -2080,14 +2080,14 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>b70d64270865ffdb564b96de6937670c517bf091abeff4cca16ed4e76111c722</t>
+          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
         </is>
       </c>
     </row>
@@ -2116,14 +2116,14 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>b70d64270865ffdb564b96de6937670c517bf091abeff4cca16ed4e76111c722</t>
+          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
         </is>
       </c>
     </row>
@@ -2152,14 +2152,14 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>b70d64270865ffdb564b96de6937670c517bf091abeff4cca16ed4e76111c722</t>
+          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
         </is>
       </c>
     </row>
@@ -2188,14 +2188,14 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>07544735417a0a092735f93a2c842eb50077c396f30faae1529120e9c10f7888</t>
+          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>07544735417a0a092735f93a2c842eb50077c396f30faae1529120e9c10f7888</t>
+          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
         </is>
       </c>
     </row>
@@ -2260,14 +2260,14 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>07544735417a0a092735f93a2c842eb50077c396f30faae1529120e9c10f7888</t>
+          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
         </is>
       </c>
     </row>
@@ -2296,14 +2296,14 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>07544735417a0a092735f93a2c842eb50077c396f30faae1529120e9c10f7888</t>
+          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
         </is>
       </c>
     </row>
@@ -2332,14 +2332,14 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>07544735417a0a092735f93a2c842eb50077c396f30faae1529120e9c10f7888</t>
+          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
         </is>
       </c>
     </row>
@@ -2368,14 +2368,14 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>07544735417a0a092735f93a2c842eb50077c396f30faae1529120e9c10f7888</t>
+          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
         </is>
       </c>
     </row>
@@ -2404,14 +2404,14 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G52" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>31fe45752275c312266d3475088c18032d2eeb774dd11d5d946ce1fd8de5317b</t>
+          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
         </is>
       </c>
     </row>
@@ -2440,14 +2440,14 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G53" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>31fe45752275c312266d3475088c18032d2eeb774dd11d5d946ce1fd8de5317b</t>
+          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
         </is>
       </c>
     </row>
@@ -2476,14 +2476,14 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G54" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>31fe45752275c312266d3475088c18032d2eeb774dd11d5d946ce1fd8de5317b</t>
+          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
         </is>
       </c>
     </row>
@@ -2512,14 +2512,14 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G55" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>31fe45752275c312266d3475088c18032d2eeb774dd11d5d946ce1fd8de5317b</t>
+          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
         </is>
       </c>
     </row>
@@ -2548,14 +2548,14 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G56" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>31fe45752275c312266d3475088c18032d2eeb774dd11d5d946ce1fd8de5317b</t>
+          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
         </is>
       </c>
     </row>
@@ -2584,14 +2584,14 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G57" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>31fe45752275c312266d3475088c18032d2eeb774dd11d5d946ce1fd8de5317b</t>
+          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>11b1ff478075157d7a09ca083eb2af4e0742c95e41b2eeb4ef2387e605bd4e7f</t>
+          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
         </is>
       </c>
     </row>
@@ -2656,14 +2656,14 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>11b1ff478075157d7a09ca083eb2af4e0742c95e41b2eeb4ef2387e605bd4e7f</t>
+          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
         </is>
       </c>
     </row>
@@ -2692,14 +2692,14 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G60" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>11b1ff478075157d7a09ca083eb2af4e0742c95e41b2eeb4ef2387e605bd4e7f</t>
+          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
         </is>
       </c>
     </row>
@@ -2728,14 +2728,14 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G61" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>11b1ff478075157d7a09ca083eb2af4e0742c95e41b2eeb4ef2387e605bd4e7f</t>
+          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
         </is>
       </c>
     </row>
@@ -2764,14 +2764,14 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>11b1ff478075157d7a09ca083eb2af4e0742c95e41b2eeb4ef2387e605bd4e7f</t>
+          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
         </is>
       </c>
     </row>
@@ -2800,14 +2800,14 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G63" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>11b1ff478075157d7a09ca083eb2af4e0742c95e41b2eeb4ef2387e605bd4e7f</t>
+          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
         </is>
       </c>
     </row>
@@ -2836,14 +2836,14 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>11b1ff478075157d7a09ca083eb2af4e0742c95e41b2eeb4ef2387e605bd4e7f</t>
+          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
         </is>
       </c>
     </row>
@@ -2872,14 +2872,14 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>11b1ff478075157d7a09ca083eb2af4e0742c95e41b2eeb4ef2387e605bd4e7f</t>
+          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
         </is>
       </c>
     </row>
@@ -2908,14 +2908,14 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>096fdbca21dad09fdc080b8947f55e91ec9101bfed04566eae1f91efb269cd80</t>
+          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
         </is>
       </c>
     </row>
@@ -2944,14 +2944,14 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>096fdbca21dad09fdc080b8947f55e91ec9101bfed04566eae1f91efb269cd80</t>
+          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
         </is>
       </c>
     </row>
@@ -2980,14 +2980,14 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G68" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>096fdbca21dad09fdc080b8947f55e91ec9101bfed04566eae1f91efb269cd80</t>
+          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>096fdbca21dad09fdc080b8947f55e91ec9101bfed04566eae1f91efb269cd80</t>
+          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
         </is>
       </c>
     </row>
@@ -3052,14 +3052,14 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G70" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>096fdbca21dad09fdc080b8947f55e91ec9101bfed04566eae1f91efb269cd80</t>
+          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
         </is>
       </c>
     </row>
@@ -3088,14 +3088,14 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>096fdbca21dad09fdc080b8947f55e91ec9101bfed04566eae1f91efb269cd80</t>
+          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
         </is>
       </c>
     </row>
@@ -3124,14 +3124,14 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>096fdbca21dad09fdc080b8947f55e91ec9101bfed04566eae1f91efb269cd80</t>
+          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
         </is>
       </c>
     </row>
@@ -3160,14 +3160,14 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>096fdbca21dad09fdc080b8947f55e91ec9101bfed04566eae1f91efb269cd80</t>
+          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
         </is>
       </c>
     </row>
@@ -3196,14 +3196,14 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>7460c9d33a4ca557fb2810a2dd40a3ae7d51ea331532a2fd7e740f1f539cbb1a</t>
+          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
         </is>
       </c>
     </row>
@@ -3232,14 +3232,14 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>7460c9d33a4ca557fb2810a2dd40a3ae7d51ea331532a2fd7e740f1f539cbb1a</t>
+          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
         </is>
       </c>
     </row>
@@ -3268,14 +3268,14 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G76" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>7460c9d33a4ca557fb2810a2dd40a3ae7d51ea331532a2fd7e740f1f539cbb1a</t>
+          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
         </is>
       </c>
     </row>
@@ -3304,14 +3304,14 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>7460c9d33a4ca557fb2810a2dd40a3ae7d51ea331532a2fd7e740f1f539cbb1a</t>
+          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
         </is>
       </c>
     </row>
@@ -3340,14 +3340,14 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G78" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>7460c9d33a4ca557fb2810a2dd40a3ae7d51ea331532a2fd7e740f1f539cbb1a</t>
+          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
         </is>
       </c>
     </row>
@@ -3376,14 +3376,14 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G79" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>7460c9d33a4ca557fb2810a2dd40a3ae7d51ea331532a2fd7e740f1f539cbb1a</t>
+          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
         </is>
       </c>
     </row>
@@ -3412,14 +3412,14 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G80" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>7460c9d33a4ca557fb2810a2dd40a3ae7d51ea331532a2fd7e740f1f539cbb1a</t>
+          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
         </is>
       </c>
     </row>
@@ -3448,14 +3448,14 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>7460c9d33a4ca557fb2810a2dd40a3ae7d51ea331532a2fd7e740f1f539cbb1a</t>
+          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
         </is>
       </c>
     </row>
@@ -3484,14 +3484,14 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G82" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>f4543cc5723954d148b98a4c0b21d99a579f19928ac42328a5674e9253f384c7</t>
+          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
         </is>
       </c>
     </row>
@@ -3520,14 +3520,14 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G83" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>f4543cc5723954d148b98a4c0b21d99a579f19928ac42328a5674e9253f384c7</t>
+          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
         </is>
       </c>
     </row>
@@ -3556,14 +3556,14 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G84" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>f4543cc5723954d148b98a4c0b21d99a579f19928ac42328a5674e9253f384c7</t>
+          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
         </is>
       </c>
     </row>
@@ -3592,14 +3592,14 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G85" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>f4543cc5723954d148b98a4c0b21d99a579f19928ac42328a5674e9253f384c7</t>
+          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
         </is>
       </c>
     </row>
@@ -3628,14 +3628,14 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G86" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>f4543cc5723954d148b98a4c0b21d99a579f19928ac42328a5674e9253f384c7</t>
+          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
         </is>
       </c>
     </row>
@@ -3664,14 +3664,14 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G87" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>f4543cc5723954d148b98a4c0b21d99a579f19928ac42328a5674e9253f384c7</t>
+          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
         </is>
       </c>
     </row>
@@ -3700,14 +3700,14 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G88" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>f4543cc5723954d148b98a4c0b21d99a579f19928ac42328a5674e9253f384c7</t>
+          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
         </is>
       </c>
     </row>
@@ -3736,14 +3736,14 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G89" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>f4543cc5723954d148b98a4c0b21d99a579f19928ac42328a5674e9253f384c7</t>
+          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
         </is>
       </c>
     </row>
@@ -3772,14 +3772,14 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>d893a26f150b5f3a54ac28c974cb54bae50bc51c02b006ffe2dc1677e9e01857</t>
+          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G91" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>d893a26f150b5f3a54ac28c974cb54bae50bc51c02b006ffe2dc1677e9e01857</t>
+          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
         </is>
       </c>
     </row>
@@ -3844,14 +3844,14 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G92" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>d893a26f150b5f3a54ac28c974cb54bae50bc51c02b006ffe2dc1677e9e01857</t>
+          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
         </is>
       </c>
     </row>
@@ -3880,14 +3880,14 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G93" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>d893a26f150b5f3a54ac28c974cb54bae50bc51c02b006ffe2dc1677e9e01857</t>
+          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
         </is>
       </c>
     </row>
@@ -3916,14 +3916,14 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>d893a26f150b5f3a54ac28c974cb54bae50bc51c02b006ffe2dc1677e9e01857</t>
+          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
         </is>
       </c>
     </row>
@@ -3952,14 +3952,14 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G95" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>d893a26f150b5f3a54ac28c974cb54bae50bc51c02b006ffe2dc1677e9e01857</t>
+          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
         </is>
       </c>
     </row>
@@ -3988,14 +3988,14 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>32a983c3de90c315456f77ae72ca6346484e8cb764c67b5eb1361614d4df1e54</t>
+          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
         </is>
       </c>
     </row>
@@ -4024,14 +4024,14 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G97" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>32a983c3de90c315456f77ae72ca6346484e8cb764c67b5eb1361614d4df1e54</t>
+          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
         </is>
       </c>
     </row>
@@ -4060,14 +4060,14 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G98" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>32a983c3de90c315456f77ae72ca6346484e8cb764c67b5eb1361614d4df1e54</t>
+          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
         </is>
       </c>
     </row>
@@ -4096,14 +4096,14 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>32a983c3de90c315456f77ae72ca6346484e8cb764c67b5eb1361614d4df1e54</t>
+          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
         </is>
       </c>
     </row>
@@ -4132,14 +4132,14 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G100" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>32a983c3de90c315456f77ae72ca6346484e8cb764c67b5eb1361614d4df1e54</t>
+          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
         </is>
       </c>
     </row>
@@ -4168,14 +4168,14 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G101" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>32a983c3de90c315456f77ae72ca6346484e8cb764c67b5eb1361614d4df1e54</t>
+          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G102" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>5c7e7ce2375ec24964030e2246dc3eddc575666e2bf15dd5db90a12c55720ce8</t>
+          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
         </is>
       </c>
     </row>
@@ -4240,14 +4240,14 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G103" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>5c7e7ce2375ec24964030e2246dc3eddc575666e2bf15dd5db90a12c55720ce8</t>
+          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
         </is>
       </c>
     </row>
@@ -4276,14 +4276,14 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G104" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5c7e7ce2375ec24964030e2246dc3eddc575666e2bf15dd5db90a12c55720ce8</t>
+          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
         </is>
       </c>
     </row>
@@ -4312,14 +4312,14 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G105" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>5c7e7ce2375ec24964030e2246dc3eddc575666e2bf15dd5db90a12c55720ce8</t>
+          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
         </is>
       </c>
     </row>
@@ -4348,14 +4348,14 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G106" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>5c7e7ce2375ec24964030e2246dc3eddc575666e2bf15dd5db90a12c55720ce8</t>
+          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
         </is>
       </c>
     </row>
@@ -4384,14 +4384,14 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G107" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>5c7e7ce2375ec24964030e2246dc3eddc575666e2bf15dd5db90a12c55720ce8</t>
+          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
         </is>
       </c>
     </row>
@@ -4420,14 +4420,14 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G108" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>360fa169ad1aa5ded2532f60c6cdb16fa998a78bad6b04b07a17e5d066159311</t>
+          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
         </is>
       </c>
     </row>
@@ -4456,14 +4456,14 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G109" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>360fa169ad1aa5ded2532f60c6cdb16fa998a78bad6b04b07a17e5d066159311</t>
+          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
         </is>
       </c>
     </row>
@@ -4492,14 +4492,14 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G110" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>360fa169ad1aa5ded2532f60c6cdb16fa998a78bad6b04b07a17e5d066159311</t>
+          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
         </is>
       </c>
     </row>
@@ -4528,14 +4528,14 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G111" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>360fa169ad1aa5ded2532f60c6cdb16fa998a78bad6b04b07a17e5d066159311</t>
+          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
         </is>
       </c>
     </row>
@@ -4564,14 +4564,14 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G112" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>360fa169ad1aa5ded2532f60c6cdb16fa998a78bad6b04b07a17e5d066159311</t>
+          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G113" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>360fa169ad1aa5ded2532f60c6cdb16fa998a78bad6b04b07a17e5d066159311</t>
+          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
         </is>
       </c>
     </row>
@@ -4636,14 +4636,14 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G114" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ff5d44f842cb07fe96dde958a39c85a52f99b7acbd5389f3a2e5c5323586907c</t>
+          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
         </is>
       </c>
     </row>
@@ -4672,14 +4672,14 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G115" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ff5d44f842cb07fe96dde958a39c85a52f99b7acbd5389f3a2e5c5323586907c</t>
+          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
         </is>
       </c>
     </row>
@@ -4708,14 +4708,14 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G116" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ff5d44f842cb07fe96dde958a39c85a52f99b7acbd5389f3a2e5c5323586907c</t>
+          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
         </is>
       </c>
     </row>
@@ -4744,14 +4744,14 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G117" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>ff5d44f842cb07fe96dde958a39c85a52f99b7acbd5389f3a2e5c5323586907c</t>
+          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
         </is>
       </c>
     </row>
@@ -4780,14 +4780,14 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G118" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ff5d44f842cb07fe96dde958a39c85a52f99b7acbd5389f3a2e5c5323586907c</t>
+          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
         </is>
       </c>
     </row>
@@ -4816,14 +4816,14 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G119" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>ff5d44f842cb07fe96dde958a39c85a52f99b7acbd5389f3a2e5c5323586907c</t>
+          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
         </is>
       </c>
     </row>
@@ -4852,14 +4852,14 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G120" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>ff5d44f842cb07fe96dde958a39c85a52f99b7acbd5389f3a2e5c5323586907c</t>
+          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
         </is>
       </c>
     </row>
@@ -4888,14 +4888,14 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G121" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ff5d44f842cb07fe96dde958a39c85a52f99b7acbd5389f3a2e5c5323586907c</t>
+          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
         </is>
       </c>
     </row>
@@ -4924,14 +4924,14 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G122" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>b9f29dd38f58f8fb9119d60b3e3c4c8328b66c311674ec0d460bc153477fbd77</t>
+          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
         </is>
       </c>
     </row>
@@ -4960,14 +4960,14 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G123" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>b9f29dd38f58f8fb9119d60b3e3c4c8328b66c311674ec0d460bc153477fbd77</t>
+          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G124" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>b9f29dd38f58f8fb9119d60b3e3c4c8328b66c311674ec0d460bc153477fbd77</t>
+          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
         </is>
       </c>
     </row>
@@ -5032,14 +5032,14 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G125" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>b9f29dd38f58f8fb9119d60b3e3c4c8328b66c311674ec0d460bc153477fbd77</t>
+          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
         </is>
       </c>
     </row>
@@ -5068,14 +5068,14 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G126" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>b9f29dd38f58f8fb9119d60b3e3c4c8328b66c311674ec0d460bc153477fbd77</t>
+          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
         </is>
       </c>
     </row>
@@ -5104,14 +5104,14 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G127" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>b9f29dd38f58f8fb9119d60b3e3c4c8328b66c311674ec0d460bc153477fbd77</t>
+          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
         </is>
       </c>
     </row>
@@ -5140,14 +5140,14 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G128" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>b9f29dd38f58f8fb9119d60b3e3c4c8328b66c311674ec0d460bc153477fbd77</t>
+          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
         </is>
       </c>
     </row>
@@ -5176,14 +5176,14 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G129" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>b9f29dd38f58f8fb9119d60b3e3c4c8328b66c311674ec0d460bc153477fbd77</t>
+          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
         </is>
       </c>
     </row>
@@ -5212,14 +5212,14 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>c1b688c26e3aa75cdb6affbe8097a9b360d3c74da413232e13bdccde7f62e3bf</t>
+          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
         </is>
       </c>
     </row>
@@ -5248,14 +5248,14 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>c1b688c26e3aa75cdb6affbe8097a9b360d3c74da413232e13bdccde7f62e3bf</t>
+          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
         </is>
       </c>
     </row>
@@ -5284,14 +5284,14 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>c1b688c26e3aa75cdb6affbe8097a9b360d3c74da413232e13bdccde7f62e3bf</t>
+          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
         </is>
       </c>
     </row>
@@ -5320,14 +5320,14 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G133" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>c1b688c26e3aa75cdb6affbe8097a9b360d3c74da413232e13bdccde7f62e3bf</t>
+          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
         </is>
       </c>
     </row>
@@ -5356,14 +5356,14 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G134" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>c1b688c26e3aa75cdb6affbe8097a9b360d3c74da413232e13bdccde7f62e3bf</t>
+          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G135" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>c1b688c26e3aa75cdb6affbe8097a9b360d3c74da413232e13bdccde7f62e3bf</t>
+          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
         </is>
       </c>
     </row>
@@ -5428,14 +5428,14 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G136" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>c1b688c26e3aa75cdb6affbe8097a9b360d3c74da413232e13bdccde7f62e3bf</t>
+          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
         </is>
       </c>
     </row>
@@ -5464,14 +5464,14 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>c1b688c26e3aa75cdb6affbe8097a9b360d3c74da413232e13bdccde7f62e3bf</t>
+          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
         </is>
       </c>
     </row>
@@ -5500,14 +5500,14 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G138" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>6131e2c4548939e1a3aef22cd0e94c79af9e8f97fd7f0a3b8956e959130d5036</t>
+          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
         </is>
       </c>
     </row>
@@ -5536,14 +5536,14 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G139" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>6131e2c4548939e1a3aef22cd0e94c79af9e8f97fd7f0a3b8956e959130d5036</t>
+          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
         </is>
       </c>
     </row>
@@ -5572,14 +5572,14 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G140" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>6131e2c4548939e1a3aef22cd0e94c79af9e8f97fd7f0a3b8956e959130d5036</t>
+          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
         </is>
       </c>
     </row>
@@ -5608,14 +5608,14 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G141" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>6131e2c4548939e1a3aef22cd0e94c79af9e8f97fd7f0a3b8956e959130d5036</t>
+          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
         </is>
       </c>
     </row>
@@ -5644,14 +5644,14 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G142" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>6131e2c4548939e1a3aef22cd0e94c79af9e8f97fd7f0a3b8956e959130d5036</t>
+          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
         </is>
       </c>
     </row>
@@ -5680,14 +5680,14 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G143" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>6131e2c4548939e1a3aef22cd0e94c79af9e8f97fd7f0a3b8956e959130d5036</t>
+          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
         </is>
       </c>
     </row>
@@ -5716,14 +5716,14 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G144" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>6131e2c4548939e1a3aef22cd0e94c79af9e8f97fd7f0a3b8956e959130d5036</t>
+          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
         </is>
       </c>
     </row>
@@ -5752,14 +5752,14 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G145" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>6131e2c4548939e1a3aef22cd0e94c79af9e8f97fd7f0a3b8956e959130d5036</t>
+          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G146" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>caf07e379671e28d0e05031220f9a35e0bdaafa76dc05a883009ae3527ef0922</t>
+          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
         </is>
       </c>
     </row>
@@ -5824,14 +5824,14 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G147" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>caf07e379671e28d0e05031220f9a35e0bdaafa76dc05a883009ae3527ef0922</t>
+          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
         </is>
       </c>
     </row>
@@ -5860,14 +5860,14 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G148" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>caf07e379671e28d0e05031220f9a35e0bdaafa76dc05a883009ae3527ef0922</t>
+          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
         </is>
       </c>
     </row>
@@ -5896,14 +5896,14 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G149" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>caf07e379671e28d0e05031220f9a35e0bdaafa76dc05a883009ae3527ef0922</t>
+          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
         </is>
       </c>
     </row>
@@ -5932,14 +5932,14 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G150" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>caf07e379671e28d0e05031220f9a35e0bdaafa76dc05a883009ae3527ef0922</t>
+          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
         </is>
       </c>
     </row>
@@ -5968,14 +5968,14 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G151" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>caf07e379671e28d0e05031220f9a35e0bdaafa76dc05a883009ae3527ef0922</t>
+          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
         </is>
       </c>
     </row>
@@ -6004,14 +6004,14 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G152" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>873d8c2d35f076b0c4e1fde8b4f72164369e1db6f193f2842d24239fcea1faeb</t>
+          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
         </is>
       </c>
     </row>
@@ -6040,14 +6040,14 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G153" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>873d8c2d35f076b0c4e1fde8b4f72164369e1db6f193f2842d24239fcea1faeb</t>
+          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
         </is>
       </c>
     </row>
@@ -6076,14 +6076,14 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G154" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>873d8c2d35f076b0c4e1fde8b4f72164369e1db6f193f2842d24239fcea1faeb</t>
+          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
         </is>
       </c>
     </row>
@@ -6112,14 +6112,14 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G155" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>873d8c2d35f076b0c4e1fde8b4f72164369e1db6f193f2842d24239fcea1faeb</t>
+          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
         </is>
       </c>
     </row>
@@ -6148,14 +6148,14 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G156" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>873d8c2d35f076b0c4e1fde8b4f72164369e1db6f193f2842d24239fcea1faeb</t>
+          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G157" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>873d8c2d35f076b0c4e1fde8b4f72164369e1db6f193f2842d24239fcea1faeb</t>
+          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
         </is>
       </c>
     </row>
@@ -6220,14 +6220,14 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G158" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4fd160a8a4abedc3f969b516b4b6e7d75b0cd59232fc43032f3f1df2fcae38c0</t>
+          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
         </is>
       </c>
     </row>
@@ -6256,14 +6256,14 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G159" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>4fd160a8a4abedc3f969b516b4b6e7d75b0cd59232fc43032f3f1df2fcae38c0</t>
+          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
         </is>
       </c>
     </row>
@@ -6292,14 +6292,14 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G160" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4fd160a8a4abedc3f969b516b4b6e7d75b0cd59232fc43032f3f1df2fcae38c0</t>
+          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
         </is>
       </c>
     </row>
@@ -6328,14 +6328,14 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G161" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4fd160a8a4abedc3f969b516b4b6e7d75b0cd59232fc43032f3f1df2fcae38c0</t>
+          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
         </is>
       </c>
     </row>
@@ -6364,14 +6364,14 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G162" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>4fd160a8a4abedc3f969b516b4b6e7d75b0cd59232fc43032f3f1df2fcae38c0</t>
+          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
         </is>
       </c>
     </row>
@@ -6400,14 +6400,14 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G163" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>4fd160a8a4abedc3f969b516b4b6e7d75b0cd59232fc43032f3f1df2fcae38c0</t>
+          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
         </is>
       </c>
     </row>
@@ -6436,14 +6436,14 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G164" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>54e7016597a53a47ac0b41c94951b9e1894b77e137f5417929952542bcbdae11</t>
+          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
         </is>
       </c>
     </row>
@@ -6472,14 +6472,14 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G165" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>54e7016597a53a47ac0b41c94951b9e1894b77e137f5417929952542bcbdae11</t>
+          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
         </is>
       </c>
     </row>
@@ -6508,14 +6508,14 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G166" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>54e7016597a53a47ac0b41c94951b9e1894b77e137f5417929952542bcbdae11</t>
+          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
         </is>
       </c>
     </row>
@@ -6544,14 +6544,14 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G167" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>54e7016597a53a47ac0b41c94951b9e1894b77e137f5417929952542bcbdae11</t>
+          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G168" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>54e7016597a53a47ac0b41c94951b9e1894b77e137f5417929952542bcbdae11</t>
+          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
         </is>
       </c>
     </row>
@@ -6616,14 +6616,14 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G169" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>54e7016597a53a47ac0b41c94951b9e1894b77e137f5417929952542bcbdae11</t>
+          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
         </is>
       </c>
     </row>
@@ -6652,14 +6652,14 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G170" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>570b822b200c17ecda5db6f81403d0ee023b19db1c53e7152962aab34bb5897e</t>
+          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
         </is>
       </c>
     </row>
@@ -6688,14 +6688,14 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G171" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>570b822b200c17ecda5db6f81403d0ee023b19db1c53e7152962aab34bb5897e</t>
+          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
         </is>
       </c>
     </row>
@@ -6724,14 +6724,14 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G172" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>570b822b200c17ecda5db6f81403d0ee023b19db1c53e7152962aab34bb5897e</t>
+          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
         </is>
       </c>
     </row>
@@ -6760,14 +6760,14 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G173" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>570b822b200c17ecda5db6f81403d0ee023b19db1c53e7152962aab34bb5897e</t>
+          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
         </is>
       </c>
     </row>
@@ -6796,14 +6796,14 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G174" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>570b822b200c17ecda5db6f81403d0ee023b19db1c53e7152962aab34bb5897e</t>
+          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
         </is>
       </c>
     </row>
@@ -6832,14 +6832,14 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G175" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>570b822b200c17ecda5db6f81403d0ee023b19db1c53e7152962aab34bb5897e</t>
+          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
         </is>
       </c>
     </row>
@@ -6868,14 +6868,14 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G176" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>570b822b200c17ecda5db6f81403d0ee023b19db1c53e7152962aab34bb5897e</t>
+          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
         </is>
       </c>
     </row>
@@ -6904,14 +6904,14 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>4299</v>
+        <v>4187</v>
       </c>
       <c r="G177" t="n">
-        <v>0.4012132524498367</v>
+        <v>0.3907606159589361</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>570b822b200c17ecda5db6f81403d0ee023b19db1c53e7152962aab34bb5897e</t>
+          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
         </is>
       </c>
     </row>
@@ -6940,14 +6940,14 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G178" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2648e722aa6f1e9f40e298039593ebbffdd4b5080c15637f7b6a6dfacd8835a7</t>
+          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G179" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2648e722aa6f1e9f40e298039593ebbffdd4b5080c15637f7b6a6dfacd8835a7</t>
+          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
         </is>
       </c>
     </row>
@@ -7012,14 +7012,14 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G180" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2648e722aa6f1e9f40e298039593ebbffdd4b5080c15637f7b6a6dfacd8835a7</t>
+          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
         </is>
       </c>
     </row>
@@ -7048,14 +7048,14 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G181" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2648e722aa6f1e9f40e298039593ebbffdd4b5080c15637f7b6a6dfacd8835a7</t>
+          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
         </is>
       </c>
     </row>
@@ -7084,14 +7084,14 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G182" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2648e722aa6f1e9f40e298039593ebbffdd4b5080c15637f7b6a6dfacd8835a7</t>
+          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
         </is>
       </c>
     </row>
@@ -7120,14 +7120,14 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G183" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2648e722aa6f1e9f40e298039593ebbffdd4b5080c15637f7b6a6dfacd8835a7</t>
+          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
         </is>
       </c>
     </row>
@@ -7156,14 +7156,14 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G184" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2648e722aa6f1e9f40e298039593ebbffdd4b5080c15637f7b6a6dfacd8835a7</t>
+          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
         </is>
       </c>
     </row>
@@ -7192,14 +7192,14 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2942</v>
+        <v>2972</v>
       </c>
       <c r="G185" t="n">
-        <v>0.4384500745156483</v>
+        <v>0.4429210134128167</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2648e722aa6f1e9f40e298039593ebbffdd4b5080c15637f7b6a6dfacd8835a7</t>
+          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
         </is>
       </c>
     </row>
@@ -7228,14 +7228,14 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G186" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>b5847837129ef14ce4883c1e66be9a93befbbfc1c3aaf7c13d5b57a5a8078fb8</t>
+          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
         </is>
       </c>
     </row>
@@ -7264,14 +7264,14 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G187" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>b5847837129ef14ce4883c1e66be9a93befbbfc1c3aaf7c13d5b57a5a8078fb8</t>
+          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
         </is>
       </c>
     </row>
@@ -7300,14 +7300,14 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G188" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>b5847837129ef14ce4883c1e66be9a93befbbfc1c3aaf7c13d5b57a5a8078fb8</t>
+          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
         </is>
       </c>
     </row>
@@ -7336,14 +7336,14 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G189" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>b5847837129ef14ce4883c1e66be9a93befbbfc1c3aaf7c13d5b57a5a8078fb8</t>
+          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G190" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>b5847837129ef14ce4883c1e66be9a93befbbfc1c3aaf7c13d5b57a5a8078fb8</t>
+          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
         </is>
       </c>
     </row>
@@ -7408,14 +7408,14 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G191" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>b5847837129ef14ce4883c1e66be9a93befbbfc1c3aaf7c13d5b57a5a8078fb8</t>
+          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
         </is>
       </c>
     </row>
@@ -7444,14 +7444,14 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G192" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>b5847837129ef14ce4883c1e66be9a93befbbfc1c3aaf7c13d5b57a5a8078fb8</t>
+          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
         </is>
       </c>
     </row>
@@ -7480,14 +7480,14 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>3588</v>
+        <v>3664</v>
       </c>
       <c r="G193" t="n">
-        <v>0.4221176470588235</v>
+        <v>0.4310588235294118</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>b5847837129ef14ce4883c1e66be9a93befbbfc1c3aaf7c13d5b57a5a8078fb8</t>
+          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
         </is>
       </c>
     </row>
@@ -7516,14 +7516,14 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G194" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>160cd2c8a9036edfbd154f3f97464c033d07190fe805c98a00d02f95acbd673b</t>
+          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
         </is>
       </c>
     </row>
@@ -7552,14 +7552,14 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G195" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>160cd2c8a9036edfbd154f3f97464c033d07190fe805c98a00d02f95acbd673b</t>
+          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
         </is>
       </c>
     </row>
@@ -7588,14 +7588,14 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G196" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>160cd2c8a9036edfbd154f3f97464c033d07190fe805c98a00d02f95acbd673b</t>
+          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
         </is>
       </c>
     </row>
@@ -7624,14 +7624,14 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G197" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>160cd2c8a9036edfbd154f3f97464c033d07190fe805c98a00d02f95acbd673b</t>
+          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
         </is>
       </c>
     </row>
@@ -7660,14 +7660,14 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G198" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>160cd2c8a9036edfbd154f3f97464c033d07190fe805c98a00d02f95acbd673b</t>
+          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
         </is>
       </c>
     </row>
@@ -7696,14 +7696,14 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G199" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>160cd2c8a9036edfbd154f3f97464c033d07190fe805c98a00d02f95acbd673b</t>
+          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
         </is>
       </c>
     </row>
@@ -7732,14 +7732,14 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G200" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>160cd2c8a9036edfbd154f3f97464c033d07190fe805c98a00d02f95acbd673b</t>
+          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3590</v>
+        <v>3597</v>
       </c>
       <c r="G201" t="n">
-        <v>0.450835112394826</v>
+        <v>0.4517141780735904</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>160cd2c8a9036edfbd154f3f97464c033d07190fe805c98a00d02f95acbd673b</t>
+          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
         </is>
       </c>
     </row>
@@ -7804,14 +7804,14 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G202" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>9ece59ec27f455666da991cfcf0a3d3b90a5a4a8ba27b68bec90d281f4a1f13d</t>
+          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
         </is>
       </c>
     </row>
@@ -7840,14 +7840,14 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G203" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>9ece59ec27f455666da991cfcf0a3d3b90a5a4a8ba27b68bec90d281f4a1f13d</t>
+          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
         </is>
       </c>
     </row>
@@ -7876,14 +7876,14 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G204" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>9ece59ec27f455666da991cfcf0a3d3b90a5a4a8ba27b68bec90d281f4a1f13d</t>
+          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
         </is>
       </c>
     </row>
@@ -7912,14 +7912,14 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G205" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>9ece59ec27f455666da991cfcf0a3d3b90a5a4a8ba27b68bec90d281f4a1f13d</t>
+          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
         </is>
       </c>
     </row>
@@ -7948,14 +7948,14 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G206" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>9ece59ec27f455666da991cfcf0a3d3b90a5a4a8ba27b68bec90d281f4a1f13d</t>
+          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
         </is>
       </c>
     </row>
@@ -7984,14 +7984,14 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="G207" t="n">
-        <v>0.4669037199124726</v>
+        <v>0.4659463894967177</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>9ece59ec27f455666da991cfcf0a3d3b90a5a4a8ba27b68bec90d281f4a1f13d</t>
+          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
         </is>
       </c>
     </row>
@@ -8020,14 +8020,14 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G208" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>8b29651ae84a61d32d0280a09a05a99ef8c429e71b158b38ea283b1cecd696da</t>
+          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
         </is>
       </c>
     </row>
@@ -8056,14 +8056,14 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G209" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>8b29651ae84a61d32d0280a09a05a99ef8c429e71b158b38ea283b1cecd696da</t>
+          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
         </is>
       </c>
     </row>
@@ -8092,14 +8092,14 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G210" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>8b29651ae84a61d32d0280a09a05a99ef8c429e71b158b38ea283b1cecd696da</t>
+          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
         </is>
       </c>
     </row>
@@ -8128,14 +8128,14 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G211" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>8b29651ae84a61d32d0280a09a05a99ef8c429e71b158b38ea283b1cecd696da</t>
+          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G212" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>8b29651ae84a61d32d0280a09a05a99ef8c429e71b158b38ea283b1cecd696da</t>
+          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
         </is>
       </c>
     </row>
@@ -8200,14 +8200,14 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>3176</v>
+        <v>3158</v>
       </c>
       <c r="G213" t="n">
-        <v>0.4533257208107336</v>
+        <v>0.4507564944333429</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>8b29651ae84a61d32d0280a09a05a99ef8c429e71b158b38ea283b1cecd696da</t>
+          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
         </is>
       </c>
     </row>
@@ -8236,14 +8236,14 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G214" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>7b432c2b5cb24c8306cd15684dad65d851a98af51348055cbe8cb45c4eba28c5</t>
+          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
         </is>
       </c>
     </row>
@@ -8272,14 +8272,14 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G215" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>7b432c2b5cb24c8306cd15684dad65d851a98af51348055cbe8cb45c4eba28c5</t>
+          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
         </is>
       </c>
     </row>
@@ -8308,14 +8308,14 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G216" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>7b432c2b5cb24c8306cd15684dad65d851a98af51348055cbe8cb45c4eba28c5</t>
+          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
         </is>
       </c>
     </row>
@@ -8344,14 +8344,14 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G217" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>7b432c2b5cb24c8306cd15684dad65d851a98af51348055cbe8cb45c4eba28c5</t>
+          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
         </is>
       </c>
     </row>
@@ -8380,14 +8380,14 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G218" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>7b432c2b5cb24c8306cd15684dad65d851a98af51348055cbe8cb45c4eba28c5</t>
+          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
         </is>
       </c>
     </row>
@@ -8416,14 +8416,14 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>2492</v>
+        <v>2474</v>
       </c>
       <c r="G219" t="n">
-        <v>0.4191757779646762</v>
+        <v>0.416148023549201</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>7b432c2b5cb24c8306cd15684dad65d851a98af51348055cbe8cb45c4eba28c5</t>
+          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
         </is>
       </c>
     </row>
@@ -8452,14 +8452,14 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G220" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>e0978e37df660f26cf92b82c6c4e88ca2fbe7a171ff13fb10fa158fd36d2ec16</t>
+          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
         </is>
       </c>
     </row>
@@ -8488,14 +8488,14 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G221" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>e0978e37df660f26cf92b82c6c4e88ca2fbe7a171ff13fb10fa158fd36d2ec16</t>
+          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
         </is>
       </c>
     </row>
@@ -8524,14 +8524,14 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G222" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>e0978e37df660f26cf92b82c6c4e88ca2fbe7a171ff13fb10fa158fd36d2ec16</t>
+          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
         </is>
       </c>
     </row>
@@ -8560,14 +8560,14 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G223" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>e0978e37df660f26cf92b82c6c4e88ca2fbe7a171ff13fb10fa158fd36d2ec16</t>
+          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
         </is>
       </c>
     </row>
@@ -8596,14 +8596,14 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G224" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>e0978e37df660f26cf92b82c6c4e88ca2fbe7a171ff13fb10fa158fd36d2ec16</t>
+          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
         </is>
       </c>
     </row>
@@ -8632,14 +8632,14 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2391</v>
+        <v>2381</v>
       </c>
       <c r="G225" t="n">
-        <v>0.464001552493693</v>
+        <v>0.46206093537745</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>e0978e37df660f26cf92b82c6c4e88ca2fbe7a171ff13fb10fa158fd36d2ec16</t>
+          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/sensitivity/D7_track_invariance.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/sensitivity/D7_track_invariance.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03935563516067416</v>
+        <v>0.04332128706688192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8507773526420304</v>
+        <v>0.8389483742925048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9784114134856962</v>
+        <v>0.9791724436804865</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01201052977953271</v>
+        <v>-0.004124947116062594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
+          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
+          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
         </is>
       </c>
     </row>
@@ -676,14 +676,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
+          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
         </is>
       </c>
     </row>
@@ -712,14 +712,14 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
+          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
         </is>
       </c>
     </row>
@@ -748,14 +748,14 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
+          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
         </is>
       </c>
     </row>
@@ -784,14 +784,14 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
+          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
         </is>
       </c>
     </row>
@@ -820,14 +820,14 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
+          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
         </is>
       </c>
     </row>
@@ -856,14 +856,14 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1442ebefdce7fdb13ca2a2bfdf771945db178653484e969d21ed8ebb4c3ae7f2</t>
+          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
         </is>
       </c>
     </row>
@@ -892,14 +892,14 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
+          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
         </is>
       </c>
     </row>
@@ -928,14 +928,14 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
+          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
         </is>
       </c>
     </row>
@@ -964,14 +964,14 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
+          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
         </is>
       </c>
     </row>
@@ -1000,14 +1000,14 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
+          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
+          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
         </is>
       </c>
     </row>
@@ -1072,14 +1072,14 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
+          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
         </is>
       </c>
     </row>
@@ -1108,14 +1108,14 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
+          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
         </is>
       </c>
     </row>
@@ -1144,14 +1144,14 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9f3d3e614339d3a9acaa0037512fa0a396b16095758fd5c532e3737eca6862c3</t>
+          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
         </is>
       </c>
     </row>
@@ -1180,14 +1180,14 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
+          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
+          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
         </is>
       </c>
     </row>
@@ -1252,14 +1252,14 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
+          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
         </is>
       </c>
     </row>
@@ -1288,14 +1288,14 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
+          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1324,14 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
+          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
         </is>
       </c>
     </row>
@@ -1360,14 +1360,14 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
+          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
         </is>
       </c>
     </row>
@@ -1396,14 +1396,14 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
+          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>e139eb92c7cd2a0b0fd1180914d65f8fe7452e73c031637bd82bf954099ddf17</t>
+          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
         </is>
       </c>
     </row>
@@ -1468,14 +1468,14 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
+          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
         </is>
       </c>
     </row>
@@ -1504,14 +1504,14 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
+          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
         </is>
       </c>
     </row>
@@ -1540,14 +1540,14 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
+          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
         </is>
       </c>
     </row>
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
+          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
         </is>
       </c>
     </row>
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
+          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
         </is>
       </c>
     </row>
@@ -1648,14 +1648,14 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
+          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
         </is>
       </c>
     </row>
@@ -1684,14 +1684,14 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
+          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
         </is>
       </c>
     </row>
@@ -1720,14 +1720,14 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>df496d2487dd991c2f05f9eb88674c0589dab3b5d021131d2b8bebedaa7ad585</t>
+          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
         </is>
       </c>
     </row>
@@ -1756,14 +1756,14 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
+          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
         </is>
       </c>
     </row>
@@ -1792,14 +1792,14 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
+          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
+          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
         </is>
       </c>
     </row>
@@ -1864,14 +1864,14 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
+          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
         </is>
       </c>
     </row>
@@ -1900,14 +1900,14 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
+          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
         </is>
       </c>
     </row>
@@ -1936,14 +1936,14 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>873f8e35e90409ace3fec02dbdddc55b476a316a09093cc6f4750ea04b6566e7</t>
+          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
         </is>
       </c>
     </row>
@@ -1972,14 +1972,14 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
+          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
         </is>
       </c>
     </row>
@@ -2008,14 +2008,14 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
+          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
         </is>
       </c>
     </row>
@@ -2044,14 +2044,14 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
+          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
         </is>
       </c>
     </row>
@@ -2080,14 +2080,14 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
+          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
         </is>
       </c>
     </row>
@@ -2116,14 +2116,14 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
+          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
         </is>
       </c>
     </row>
@@ -2152,14 +2152,14 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3d7800c333ec2ddc5cb349813782ba05a3df7c559e8d080b7e407bec99a65253</t>
+          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
         </is>
       </c>
     </row>
@@ -2188,14 +2188,14 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G46" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
+          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G47" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
+          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
         </is>
       </c>
     </row>
@@ -2260,14 +2260,14 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G48" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
+          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
         </is>
       </c>
     </row>
@@ -2296,14 +2296,14 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G49" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
+          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
         </is>
       </c>
     </row>
@@ -2332,14 +2332,14 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G50" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
+          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
         </is>
       </c>
     </row>
@@ -2368,14 +2368,14 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G51" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9576827211840e6e634a95e568609e68f795bfd8909bd7c438ac7fa48d1dfb9a</t>
+          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
         </is>
       </c>
     </row>
@@ -2404,14 +2404,14 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G52" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
+          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
         </is>
       </c>
     </row>
@@ -2440,14 +2440,14 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G53" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
+          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
         </is>
       </c>
     </row>
@@ -2476,14 +2476,14 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G54" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
+          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
         </is>
       </c>
     </row>
@@ -2512,14 +2512,14 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G55" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
+          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
         </is>
       </c>
     </row>
@@ -2548,14 +2548,14 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G56" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
+          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
         </is>
       </c>
     </row>
@@ -2584,14 +2584,14 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G57" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>738df3e126d1de1ee2e257f99067aab108ba61b583ee2f13057b4b20dca037a9</t>
+          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
+          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
         </is>
       </c>
     </row>
@@ -2656,14 +2656,14 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
+          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
         </is>
       </c>
     </row>
@@ -2692,14 +2692,14 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
+          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
         </is>
       </c>
     </row>
@@ -2728,14 +2728,14 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
+          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
         </is>
       </c>
     </row>
@@ -2764,14 +2764,14 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
+          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
         </is>
       </c>
     </row>
@@ -2800,14 +2800,14 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
+          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
         </is>
       </c>
     </row>
@@ -2836,14 +2836,14 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
+          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
         </is>
       </c>
     </row>
@@ -2872,14 +2872,14 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>607002f964f936b163dcfa7d7b01b3c17c46149c98a11d535d5f02aa31d93338</t>
+          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
         </is>
       </c>
     </row>
@@ -2908,14 +2908,14 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
+          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
         </is>
       </c>
     </row>
@@ -2944,14 +2944,14 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
+          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
         </is>
       </c>
     </row>
@@ -2980,14 +2980,14 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G68" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
+          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
+          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
         </is>
       </c>
     </row>
@@ -3052,14 +3052,14 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G70" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
+          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
         </is>
       </c>
     </row>
@@ -3088,14 +3088,14 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
+          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
         </is>
       </c>
     </row>
@@ -3124,14 +3124,14 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
+          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
         </is>
       </c>
     </row>
@@ -3160,14 +3160,14 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>aa6099ab7c2701e8fffa3691fa7a5754399d8790b3f3c9ac97595744e848eddd</t>
+          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
         </is>
       </c>
     </row>
@@ -3196,14 +3196,14 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
+          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
         </is>
       </c>
     </row>
@@ -3232,14 +3232,14 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
+          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
         </is>
       </c>
     </row>
@@ -3268,14 +3268,14 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G76" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
+          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
         </is>
       </c>
     </row>
@@ -3304,14 +3304,14 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
+          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
         </is>
       </c>
     </row>
@@ -3340,14 +3340,14 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G78" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
+          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
         </is>
       </c>
     </row>
@@ -3376,14 +3376,14 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G79" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
+          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
         </is>
       </c>
     </row>
@@ -3412,14 +3412,14 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G80" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
+          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
         </is>
       </c>
     </row>
@@ -3448,14 +3448,14 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>22ed0bad43d60eea986f0d01d884d1e26b3aa98c1785808dfbf2ff7dc560b3d9</t>
+          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
         </is>
       </c>
     </row>
@@ -3484,14 +3484,14 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
+          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
         </is>
       </c>
     </row>
@@ -3520,14 +3520,14 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
+          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
         </is>
       </c>
     </row>
@@ -3556,14 +3556,14 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G84" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
+          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
         </is>
       </c>
     </row>
@@ -3592,14 +3592,14 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G85" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
+          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
         </is>
       </c>
     </row>
@@ -3628,14 +3628,14 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
+          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
         </is>
       </c>
     </row>
@@ -3664,14 +3664,14 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G87" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
+          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
         </is>
       </c>
     </row>
@@ -3700,14 +3700,14 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G88" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
+          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
         </is>
       </c>
     </row>
@@ -3736,14 +3736,14 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G89" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>932d28b80e6a36ce2df59cc298fc99bad282a7827f27e9ca1e648b02ea03809a</t>
+          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
         </is>
       </c>
     </row>
@@ -3772,14 +3772,14 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
+          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G91" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
+          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
         </is>
       </c>
     </row>
@@ -3844,14 +3844,14 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G92" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
+          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
         </is>
       </c>
     </row>
@@ -3880,14 +3880,14 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G93" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
+          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
         </is>
       </c>
     </row>
@@ -3916,14 +3916,14 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
+          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
         </is>
       </c>
     </row>
@@ -3952,14 +3952,14 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G95" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4b4531ae2ab1ed3f82cc8cec16c72e4e102d054b15ffb3f7f8cf56e08297c402</t>
+          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
         </is>
       </c>
     </row>
@@ -3988,14 +3988,14 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
+          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
         </is>
       </c>
     </row>
@@ -4024,14 +4024,14 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G97" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
+          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
         </is>
       </c>
     </row>
@@ -4060,14 +4060,14 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G98" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
+          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
         </is>
       </c>
     </row>
@@ -4096,14 +4096,14 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
+          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
         </is>
       </c>
     </row>
@@ -4132,14 +4132,14 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G100" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
+          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
         </is>
       </c>
     </row>
@@ -4168,14 +4168,14 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G101" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>44b048ea45b3c10018b878b7d0075672ed5fa41b60e5f6777a7f920a1182ff41</t>
+          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G102" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
+          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
         </is>
       </c>
     </row>
@@ -4240,14 +4240,14 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G103" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
+          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
         </is>
       </c>
     </row>
@@ -4276,14 +4276,14 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G104" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
+          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
         </is>
       </c>
     </row>
@@ -4312,14 +4312,14 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G105" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
+          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
         </is>
       </c>
     </row>
@@ -4348,14 +4348,14 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G106" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
+          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
         </is>
       </c>
     </row>
@@ -4384,14 +4384,14 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G107" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>a58890d3081446665c30d326470659288d6ecde1e611660e8dfe470a46dd6b53</t>
+          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
         </is>
       </c>
     </row>
@@ -4420,14 +4420,14 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G108" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
+          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
         </is>
       </c>
     </row>
@@ -4456,14 +4456,14 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G109" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
+          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
         </is>
       </c>
     </row>
@@ -4492,14 +4492,14 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G110" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
+          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
         </is>
       </c>
     </row>
@@ -4528,14 +4528,14 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G111" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
+          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
         </is>
       </c>
     </row>
@@ -4564,14 +4564,14 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G112" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
+          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G113" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>b71f65bbedbe065b02d2c1abd887571e00f8259e2b3e8f06899cab017edc9aef</t>
+          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
         </is>
       </c>
     </row>
@@ -4636,14 +4636,14 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G114" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
+          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
         </is>
       </c>
     </row>
@@ -4672,14 +4672,14 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G115" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
+          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
         </is>
       </c>
     </row>
@@ -4708,14 +4708,14 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G116" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
+          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
         </is>
       </c>
     </row>
@@ -4744,14 +4744,14 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G117" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
+          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
         </is>
       </c>
     </row>
@@ -4780,14 +4780,14 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G118" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
+          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
         </is>
       </c>
     </row>
@@ -4816,14 +4816,14 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G119" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
+          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
         </is>
       </c>
     </row>
@@ -4852,14 +4852,14 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G120" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
+          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
         </is>
       </c>
     </row>
@@ -4888,14 +4888,14 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G121" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>faeb38568d9f0522bde8c2c513c44663d14ea5cbbef4f65363fd664d6c0f5479</t>
+          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
         </is>
       </c>
     </row>
@@ -4924,14 +4924,14 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G122" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
+          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
         </is>
       </c>
     </row>
@@ -4960,14 +4960,14 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G123" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
+          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G124" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
+          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
         </is>
       </c>
     </row>
@@ -5032,14 +5032,14 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G125" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
+          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
         </is>
       </c>
     </row>
@@ -5068,14 +5068,14 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G126" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
+          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
         </is>
       </c>
     </row>
@@ -5104,14 +5104,14 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G127" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
+          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
         </is>
       </c>
     </row>
@@ -5140,14 +5140,14 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G128" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
+          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
         </is>
       </c>
     </row>
@@ -5176,14 +5176,14 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G129" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>5459688a191e13dfb73315a17ae028fb7434f31d3ce66ad7e9d50bd6be3d1654</t>
+          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
         </is>
       </c>
     </row>
@@ -5212,14 +5212,14 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
+          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
         </is>
       </c>
     </row>
@@ -5248,14 +5248,14 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
+          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
         </is>
       </c>
     </row>
@@ -5284,14 +5284,14 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
+          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
         </is>
       </c>
     </row>
@@ -5320,14 +5320,14 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G133" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
+          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
         </is>
       </c>
     </row>
@@ -5356,14 +5356,14 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G134" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
+          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G135" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
+          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
         </is>
       </c>
     </row>
@@ -5428,14 +5428,14 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G136" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
+          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
         </is>
       </c>
     </row>
@@ -5464,14 +5464,14 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>852d40332404f5fe23d6c42873648e874caacf66e4cb502b826faad219d0e9f1</t>
+          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
         </is>
       </c>
     </row>
@@ -5500,14 +5500,14 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G138" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
+          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
         </is>
       </c>
     </row>
@@ -5536,14 +5536,14 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G139" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
+          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
         </is>
       </c>
     </row>
@@ -5572,14 +5572,14 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
+          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
         </is>
       </c>
     </row>
@@ -5608,14 +5608,14 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G141" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
+          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
         </is>
       </c>
     </row>
@@ -5644,14 +5644,14 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G142" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
+          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
         </is>
       </c>
     </row>
@@ -5680,14 +5680,14 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G143" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
+          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
         </is>
       </c>
     </row>
@@ -5716,14 +5716,14 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G144" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
+          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
         </is>
       </c>
     </row>
@@ -5752,14 +5752,14 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G145" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>ff529f34e6255a8fe0eb7dafd8bdede645d44fa563316f284674f23742c58713</t>
+          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G146" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
+          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
         </is>
       </c>
     </row>
@@ -5824,14 +5824,14 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G147" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
+          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
         </is>
       </c>
     </row>
@@ -5860,14 +5860,14 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G148" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
+          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
         </is>
       </c>
     </row>
@@ -5896,14 +5896,14 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G149" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
+          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
         </is>
       </c>
     </row>
@@ -5932,14 +5932,14 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G150" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
+          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
         </is>
       </c>
     </row>
@@ -5968,14 +5968,14 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G151" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>7a9393c88c1b4e3c12c17596f8251693f5cb590b53ff40f5cc94c80f0f17d8c1</t>
+          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
         </is>
       </c>
     </row>
@@ -6004,14 +6004,14 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G152" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
+          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
         </is>
       </c>
     </row>
@@ -6040,14 +6040,14 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G153" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
+          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
         </is>
       </c>
     </row>
@@ -6076,14 +6076,14 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G154" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
+          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
         </is>
       </c>
     </row>
@@ -6112,14 +6112,14 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G155" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
+          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
         </is>
       </c>
     </row>
@@ -6148,14 +6148,14 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G156" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
+          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G157" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>a34e299e49f655324937880ca46cff4a3263ab4d84160960a84b563e638d888c</t>
+          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
         </is>
       </c>
     </row>
@@ -6220,14 +6220,14 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G158" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
+          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
         </is>
       </c>
     </row>
@@ -6256,14 +6256,14 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G159" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
+          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
         </is>
       </c>
     </row>
@@ -6292,14 +6292,14 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G160" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
+          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
         </is>
       </c>
     </row>
@@ -6328,14 +6328,14 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G161" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
+          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
         </is>
       </c>
     </row>
@@ -6364,14 +6364,14 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G162" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
+          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
         </is>
       </c>
     </row>
@@ -6400,14 +6400,14 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G163" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>e441ad36f5ad4f1adc0986f76522c5e7f5eed837102923b22054552ff01228bb</t>
+          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
         </is>
       </c>
     </row>
@@ -6436,14 +6436,14 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G164" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
+          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
         </is>
       </c>
     </row>
@@ -6472,14 +6472,14 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G165" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
+          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
         </is>
       </c>
     </row>
@@ -6508,14 +6508,14 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G166" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
+          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
         </is>
       </c>
     </row>
@@ -6544,14 +6544,14 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G167" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
+          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G168" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
+          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
         </is>
       </c>
     </row>
@@ -6616,14 +6616,14 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G169" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>59ff6c367a87cee9a344bc93ffd03f5613b325226a9e1a176773c457e3f6cf96</t>
+          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
         </is>
       </c>
     </row>
@@ -6652,14 +6652,14 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G170" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
+          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
         </is>
       </c>
     </row>
@@ -6688,14 +6688,14 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G171" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
+          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
         </is>
       </c>
     </row>
@@ -6724,14 +6724,14 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G172" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
+          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
         </is>
       </c>
     </row>
@@ -6760,14 +6760,14 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G173" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
+          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
         </is>
       </c>
     </row>
@@ -6796,14 +6796,14 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G174" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
+          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
         </is>
       </c>
     </row>
@@ -6832,14 +6832,14 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G175" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
+          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
         </is>
       </c>
     </row>
@@ -6868,14 +6868,14 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G176" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
+          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
         </is>
       </c>
     </row>
@@ -6904,14 +6904,14 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>4187</v>
+        <v>5006</v>
       </c>
       <c r="G177" t="n">
-        <v>0.3907606159589361</v>
+        <v>0.4671955202986467</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>b5b1ed3632d232d06a1ba4074b786f7e861e6c271e587e2d68e93bc0b842f910</t>
+          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
         </is>
       </c>
     </row>
@@ -6940,14 +6940,14 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G178" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
+          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G179" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
+          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
         </is>
       </c>
     </row>
@@ -7012,14 +7012,14 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G180" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
+          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
         </is>
       </c>
     </row>
@@ -7048,14 +7048,14 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G181" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
+          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
         </is>
       </c>
     </row>
@@ -7084,14 +7084,14 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G182" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
+          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
         </is>
       </c>
     </row>
@@ -7120,14 +7120,14 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G183" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
+          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
         </is>
       </c>
     </row>
@@ -7156,14 +7156,14 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G184" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
+          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
         </is>
       </c>
     </row>
@@ -7192,14 +7192,14 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2972</v>
+        <v>3298</v>
       </c>
       <c r="G185" t="n">
-        <v>0.4429210134128167</v>
+        <v>0.49150521609538</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>025e9823a5ef10d5943432b657461082a988f9c32bf2809591a2f388ab696c4c</t>
+          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
         </is>
       </c>
     </row>
@@ -7228,14 +7228,14 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G186" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
+          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
         </is>
       </c>
     </row>
@@ -7264,14 +7264,14 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G187" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
+          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
         </is>
       </c>
     </row>
@@ -7300,14 +7300,14 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G188" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
+          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
         </is>
       </c>
     </row>
@@ -7336,14 +7336,14 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G189" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
+          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G190" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
+          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
         </is>
       </c>
     </row>
@@ -7408,14 +7408,14 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G191" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
+          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
         </is>
       </c>
     </row>
@@ -7444,14 +7444,14 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G192" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
+          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
         </is>
       </c>
     </row>
@@ -7480,14 +7480,14 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>3664</v>
+        <v>4061</v>
       </c>
       <c r="G193" t="n">
-        <v>0.4310588235294118</v>
+        <v>0.4777647058823529</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>a606425e59863c912e6d181b2295821ac34ba9958a52b9cebb1f35a230bbc0f1</t>
+          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
         </is>
       </c>
     </row>
@@ -7516,14 +7516,14 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G194" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
+          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
         </is>
       </c>
     </row>
@@ -7552,14 +7552,14 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G195" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
+          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
         </is>
       </c>
     </row>
@@ -7588,14 +7588,14 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G196" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
+          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
         </is>
       </c>
     </row>
@@ -7624,14 +7624,14 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G197" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
+          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
         </is>
       </c>
     </row>
@@ -7660,14 +7660,14 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G198" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
+          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
         </is>
       </c>
     </row>
@@ -7696,14 +7696,14 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G199" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
+          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
         </is>
       </c>
     </row>
@@ -7732,14 +7732,14 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G200" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
+          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3597</v>
+        <v>3844</v>
       </c>
       <c r="G201" t="n">
-        <v>0.4517141780735904</v>
+        <v>0.4827326384528444</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>855cde89d852e684fc499f39a7a615487d8a7343e81b12f589e2a6238d8893c0</t>
+          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
         </is>
       </c>
     </row>
@@ -7804,14 +7804,14 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G202" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
+          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
         </is>
       </c>
     </row>
@@ -7840,14 +7840,14 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G203" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
+          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
         </is>
       </c>
     </row>
@@ -7876,14 +7876,14 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G204" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
+          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
         </is>
       </c>
     </row>
@@ -7912,14 +7912,14 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G205" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
+          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
         </is>
       </c>
     </row>
@@ -7948,14 +7948,14 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G206" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
+          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
         </is>
       </c>
     </row>
@@ -7984,14 +7984,14 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>3407</v>
+        <v>3336</v>
       </c>
       <c r="G207" t="n">
-        <v>0.4659463894967177</v>
+        <v>0.4562363238512035</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>ba98a2b7840976bb2f4015f72e447a4c6e9a20fcf269be19219990703f583f07</t>
+          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
         </is>
       </c>
     </row>
@@ -8020,14 +8020,14 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G208" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
+          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
         </is>
       </c>
     </row>
@@ -8056,14 +8056,14 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G209" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
+          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
         </is>
       </c>
     </row>
@@ -8092,14 +8092,14 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G210" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
+          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
         </is>
       </c>
     </row>
@@ -8128,14 +8128,14 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G211" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
+          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G212" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
+          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
         </is>
       </c>
     </row>
@@ -8200,14 +8200,14 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>3158</v>
+        <v>3043</v>
       </c>
       <c r="G213" t="n">
-        <v>0.4507564944333429</v>
+        <v>0.4343419925777905</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>5a02179b84b5bcdbcf2de7388d13d6c3cc7af2a22995ca05b4e42435c3b27ef5</t>
+          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
         </is>
       </c>
     </row>
@@ -8236,14 +8236,14 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G214" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
+          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
         </is>
       </c>
     </row>
@@ -8272,14 +8272,14 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G215" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
+          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
         </is>
       </c>
     </row>
@@ -8308,14 +8308,14 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G216" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
+          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
         </is>
       </c>
     </row>
@@ -8344,14 +8344,14 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G217" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
+          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
         </is>
       </c>
     </row>
@@ -8380,14 +8380,14 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G218" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
+          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
         </is>
       </c>
     </row>
@@ -8416,14 +8416,14 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>2474</v>
+        <v>2344</v>
       </c>
       <c r="G219" t="n">
-        <v>0.416148023549201</v>
+        <v>0.3942809083263246</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>82ce6937b637fbc435ba2564f95c5993b5e7fd201b890c99606bdf817f8e0fd5</t>
+          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
         </is>
       </c>
     </row>
@@ -8452,14 +8452,14 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G220" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
+          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
         </is>
       </c>
     </row>
@@ -8488,14 +8488,14 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G221" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
+          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
         </is>
       </c>
     </row>
@@ -8524,14 +8524,14 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G222" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
+          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
         </is>
       </c>
     </row>
@@ -8560,14 +8560,14 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G223" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
+          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
         </is>
       </c>
     </row>
@@ -8596,14 +8596,14 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G224" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
+          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
         </is>
       </c>
     </row>
@@ -8632,14 +8632,14 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2381</v>
+        <v>2305</v>
       </c>
       <c r="G225" t="n">
-        <v>0.46206093537745</v>
+        <v>0.4473122452940035</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2211134ce3d3292c89d7ab0655156ed33e353a786468875a83faa3b96547e638</t>
+          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/sensitivity/D7_track_invariance.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/sensitivity/D7_track_invariance.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04332128706688192</v>
+        <v>0.04817068966358561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8389483742925048</v>
+        <v>0.8251274138495348</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9791724436804865</v>
+        <v>0.9619507138943536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004124947116062594</v>
+        <v>-0.01158745828044938</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
+          <t>28dded253e7f0a83b4ce926e5ee29a5c6f4ee9a1a826fc151a675e94be722426</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
+          <t>28dded253e7f0a83b4ce926e5ee29a5c6f4ee9a1a826fc151a675e94be722426</t>
         </is>
       </c>
     </row>
@@ -676,14 +676,14 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
+          <t>28dded253e7f0a83b4ce926e5ee29a5c6f4ee9a1a826fc151a675e94be722426</t>
         </is>
       </c>
     </row>
@@ -712,14 +712,14 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
+          <t>28dded253e7f0a83b4ce926e5ee29a5c6f4ee9a1a826fc151a675e94be722426</t>
         </is>
       </c>
     </row>
@@ -748,14 +748,14 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
+          <t>28dded253e7f0a83b4ce926e5ee29a5c6f4ee9a1a826fc151a675e94be722426</t>
         </is>
       </c>
     </row>
@@ -784,14 +784,14 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
+          <t>28dded253e7f0a83b4ce926e5ee29a5c6f4ee9a1a826fc151a675e94be722426</t>
         </is>
       </c>
     </row>
@@ -820,14 +820,14 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
+          <t>28dded253e7f0a83b4ce926e5ee29a5c6f4ee9a1a826fc151a675e94be722426</t>
         </is>
       </c>
     </row>
@@ -856,14 +856,14 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>76603eabb7246e92268533b94fc60f5fe6e7129ffbe3d10b972bea9718164604</t>
+          <t>28dded253e7f0a83b4ce926e5ee29a5c6f4ee9a1a826fc151a675e94be722426</t>
         </is>
       </c>
     </row>
@@ -892,14 +892,14 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G10" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
+          <t>184a0d8687c5af120416bb0c63edccde7fc8b29ac7397f797bf900537b24b174</t>
         </is>
       </c>
     </row>
@@ -928,14 +928,14 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G11" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
+          <t>184a0d8687c5af120416bb0c63edccde7fc8b29ac7397f797bf900537b24b174</t>
         </is>
       </c>
     </row>
@@ -964,14 +964,14 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G12" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
+          <t>184a0d8687c5af120416bb0c63edccde7fc8b29ac7397f797bf900537b24b174</t>
         </is>
       </c>
     </row>
@@ -1000,14 +1000,14 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G13" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
+          <t>184a0d8687c5af120416bb0c63edccde7fc8b29ac7397f797bf900537b24b174</t>
         </is>
       </c>
     </row>
@@ -1036,14 +1036,14 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G14" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
+          <t>184a0d8687c5af120416bb0c63edccde7fc8b29ac7397f797bf900537b24b174</t>
         </is>
       </c>
     </row>
@@ -1072,14 +1072,14 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G15" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
+          <t>184a0d8687c5af120416bb0c63edccde7fc8b29ac7397f797bf900537b24b174</t>
         </is>
       </c>
     </row>
@@ -1108,14 +1108,14 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G16" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
+          <t>184a0d8687c5af120416bb0c63edccde7fc8b29ac7397f797bf900537b24b174</t>
         </is>
       </c>
     </row>
@@ -1144,14 +1144,14 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G17" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>88362f9d53ca969c1d6518a9f2059c47559644862a519e46da972b84c1da38b8</t>
+          <t>184a0d8687c5af120416bb0c63edccde7fc8b29ac7397f797bf900537b24b174</t>
         </is>
       </c>
     </row>
@@ -1180,14 +1180,14 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
+          <t>a76cd9cb0a310336542243000b8d7ee86a7bb64ecfca9792969dd47ede15e681</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
+          <t>a76cd9cb0a310336542243000b8d7ee86a7bb64ecfca9792969dd47ede15e681</t>
         </is>
       </c>
     </row>
@@ -1252,14 +1252,14 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
+          <t>a76cd9cb0a310336542243000b8d7ee86a7bb64ecfca9792969dd47ede15e681</t>
         </is>
       </c>
     </row>
@@ -1288,14 +1288,14 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
+          <t>a76cd9cb0a310336542243000b8d7ee86a7bb64ecfca9792969dd47ede15e681</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1324,14 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
+          <t>a76cd9cb0a310336542243000b8d7ee86a7bb64ecfca9792969dd47ede15e681</t>
         </is>
       </c>
     </row>
@@ -1360,14 +1360,14 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
+          <t>a76cd9cb0a310336542243000b8d7ee86a7bb64ecfca9792969dd47ede15e681</t>
         </is>
       </c>
     </row>
@@ -1396,14 +1396,14 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
+          <t>a76cd9cb0a310336542243000b8d7ee86a7bb64ecfca9792969dd47ede15e681</t>
         </is>
       </c>
     </row>
@@ -1432,14 +1432,14 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>98b1dd272dfdbd8b2808a4580a4058d95d750b70875a3d09ff55b0d12d3bbf0f</t>
+          <t>a76cd9cb0a310336542243000b8d7ee86a7bb64ecfca9792969dd47ede15e681</t>
         </is>
       </c>
     </row>
@@ -1468,14 +1468,14 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
+          <t>a11479785ce2bbbba5992bda827f45f357f0070b34253d98de59d6b2978bd245</t>
         </is>
       </c>
     </row>
@@ -1504,14 +1504,14 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
+          <t>a11479785ce2bbbba5992bda827f45f357f0070b34253d98de59d6b2978bd245</t>
         </is>
       </c>
     </row>
@@ -1540,14 +1540,14 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
+          <t>a11479785ce2bbbba5992bda827f45f357f0070b34253d98de59d6b2978bd245</t>
         </is>
       </c>
     </row>
@@ -1576,14 +1576,14 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
+          <t>a11479785ce2bbbba5992bda827f45f357f0070b34253d98de59d6b2978bd245</t>
         </is>
       </c>
     </row>
@@ -1612,14 +1612,14 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
+          <t>a11479785ce2bbbba5992bda827f45f357f0070b34253d98de59d6b2978bd245</t>
         </is>
       </c>
     </row>
@@ -1648,14 +1648,14 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
+          <t>a11479785ce2bbbba5992bda827f45f357f0070b34253d98de59d6b2978bd245</t>
         </is>
       </c>
     </row>
@@ -1684,14 +1684,14 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
+          <t>a11479785ce2bbbba5992bda827f45f357f0070b34253d98de59d6b2978bd245</t>
         </is>
       </c>
     </row>
@@ -1720,14 +1720,14 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>b6524372cdcb05ac31cbf9220e4631cee152cfd460edba966ee3f52bd2989db0</t>
+          <t>a11479785ce2bbbba5992bda827f45f357f0070b34253d98de59d6b2978bd245</t>
         </is>
       </c>
     </row>
@@ -1756,14 +1756,14 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
+          <t>b9da7cff50307a89b3b49c712ee86372c6e22d8a5381e8ca4ea92c32210cf290</t>
         </is>
       </c>
     </row>
@@ -1792,14 +1792,14 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
+          <t>b9da7cff50307a89b3b49c712ee86372c6e22d8a5381e8ca4ea92c32210cf290</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1828,14 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
+          <t>b9da7cff50307a89b3b49c712ee86372c6e22d8a5381e8ca4ea92c32210cf290</t>
         </is>
       </c>
     </row>
@@ -1864,14 +1864,14 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
+          <t>b9da7cff50307a89b3b49c712ee86372c6e22d8a5381e8ca4ea92c32210cf290</t>
         </is>
       </c>
     </row>
@@ -1900,14 +1900,14 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
+          <t>b9da7cff50307a89b3b49c712ee86372c6e22d8a5381e8ca4ea92c32210cf290</t>
         </is>
       </c>
     </row>
@@ -1936,14 +1936,14 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>b5b740b24412b77c168f9ec99617a5359f03921096bb9ede2eaa8570f9ffcef1</t>
+          <t>b9da7cff50307a89b3b49c712ee86372c6e22d8a5381e8ca4ea92c32210cf290</t>
         </is>
       </c>
     </row>
@@ -1972,14 +1972,14 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
+          <t>04bebbf5fc9ae8095d597345d63ae9f243b03224836ee05c0684b4293e86ae58</t>
         </is>
       </c>
     </row>
@@ -2008,14 +2008,14 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
+          <t>04bebbf5fc9ae8095d597345d63ae9f243b03224836ee05c0684b4293e86ae58</t>
         </is>
       </c>
     </row>
@@ -2044,14 +2044,14 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
+          <t>04bebbf5fc9ae8095d597345d63ae9f243b03224836ee05c0684b4293e86ae58</t>
         </is>
       </c>
     </row>
@@ -2080,14 +2080,14 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
+          <t>04bebbf5fc9ae8095d597345d63ae9f243b03224836ee05c0684b4293e86ae58</t>
         </is>
       </c>
     </row>
@@ -2116,14 +2116,14 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
+          <t>04bebbf5fc9ae8095d597345d63ae9f243b03224836ee05c0684b4293e86ae58</t>
         </is>
       </c>
     </row>
@@ -2152,14 +2152,14 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18a774d731ba950324995cebbdcc9240351143bbce7f1df9787908403108bc3e</t>
+          <t>04bebbf5fc9ae8095d597345d63ae9f243b03224836ee05c0684b4293e86ae58</t>
         </is>
       </c>
     </row>
@@ -2188,14 +2188,14 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
+          <t>c98f83c5e100b7f479381ed11183486123cac4612b26e79590d280f5dbdab995</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2224,14 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
+          <t>c98f83c5e100b7f479381ed11183486123cac4612b26e79590d280f5dbdab995</t>
         </is>
       </c>
     </row>
@@ -2260,14 +2260,14 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
+          <t>c98f83c5e100b7f479381ed11183486123cac4612b26e79590d280f5dbdab995</t>
         </is>
       </c>
     </row>
@@ -2296,14 +2296,14 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
+          <t>c98f83c5e100b7f479381ed11183486123cac4612b26e79590d280f5dbdab995</t>
         </is>
       </c>
     </row>
@@ -2332,14 +2332,14 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
+          <t>c98f83c5e100b7f479381ed11183486123cac4612b26e79590d280f5dbdab995</t>
         </is>
       </c>
     </row>
@@ -2368,14 +2368,14 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>57e45269d4292d753b119fa6659703966b5ac54647ea7eab4c0e17f09978a13b</t>
+          <t>c98f83c5e100b7f479381ed11183486123cac4612b26e79590d280f5dbdab995</t>
         </is>
       </c>
     </row>
@@ -2404,14 +2404,14 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
+          <t>857e00d78a95cc47f9686be6b7274101c2a8063087a16b44b89db5b8c9a94faf</t>
         </is>
       </c>
     </row>
@@ -2440,14 +2440,14 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
+          <t>857e00d78a95cc47f9686be6b7274101c2a8063087a16b44b89db5b8c9a94faf</t>
         </is>
       </c>
     </row>
@@ -2476,14 +2476,14 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
+          <t>857e00d78a95cc47f9686be6b7274101c2a8063087a16b44b89db5b8c9a94faf</t>
         </is>
       </c>
     </row>
@@ -2512,14 +2512,14 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G55" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
+          <t>857e00d78a95cc47f9686be6b7274101c2a8063087a16b44b89db5b8c9a94faf</t>
         </is>
       </c>
     </row>
@@ -2548,14 +2548,14 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
+          <t>857e00d78a95cc47f9686be6b7274101c2a8063087a16b44b89db5b8c9a94faf</t>
         </is>
       </c>
     </row>
@@ -2584,14 +2584,14 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>63dd9a0c9fbaeb526633c90cd177524ddc8c415c41a8298cde00218637ca0d62</t>
+          <t>857e00d78a95cc47f9686be6b7274101c2a8063087a16b44b89db5b8c9a94faf</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
+          <t>d408d3041ce74b43ff62ef375bf22ffa04e8fa0e3b973d323ccea26a91b3ef38</t>
         </is>
       </c>
     </row>
@@ -2656,14 +2656,14 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
+          <t>d408d3041ce74b43ff62ef375bf22ffa04e8fa0e3b973d323ccea26a91b3ef38</t>
         </is>
       </c>
     </row>
@@ -2692,14 +2692,14 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G60" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
+          <t>d408d3041ce74b43ff62ef375bf22ffa04e8fa0e3b973d323ccea26a91b3ef38</t>
         </is>
       </c>
     </row>
@@ -2728,14 +2728,14 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G61" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
+          <t>d408d3041ce74b43ff62ef375bf22ffa04e8fa0e3b973d323ccea26a91b3ef38</t>
         </is>
       </c>
     </row>
@@ -2764,14 +2764,14 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
+          <t>d408d3041ce74b43ff62ef375bf22ffa04e8fa0e3b973d323ccea26a91b3ef38</t>
         </is>
       </c>
     </row>
@@ -2800,14 +2800,14 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G63" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
+          <t>d408d3041ce74b43ff62ef375bf22ffa04e8fa0e3b973d323ccea26a91b3ef38</t>
         </is>
       </c>
     </row>
@@ -2836,14 +2836,14 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
+          <t>d408d3041ce74b43ff62ef375bf22ffa04e8fa0e3b973d323ccea26a91b3ef38</t>
         </is>
       </c>
     </row>
@@ -2872,14 +2872,14 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>b4e7d7747a23fd15d7c53598a786da35e7130d382fd1c8c61bb78ee918f368ee</t>
+          <t>d408d3041ce74b43ff62ef375bf22ffa04e8fa0e3b973d323ccea26a91b3ef38</t>
         </is>
       </c>
     </row>
@@ -2908,14 +2908,14 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G66" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
+          <t>9d9513056702d47b1bd0bbeb48d37404a525c1ab7193926f0cf92dea38694c73</t>
         </is>
       </c>
     </row>
@@ -2944,14 +2944,14 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G67" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
+          <t>9d9513056702d47b1bd0bbeb48d37404a525c1ab7193926f0cf92dea38694c73</t>
         </is>
       </c>
     </row>
@@ -2980,14 +2980,14 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G68" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
+          <t>9d9513056702d47b1bd0bbeb48d37404a525c1ab7193926f0cf92dea38694c73</t>
         </is>
       </c>
     </row>
@@ -3016,14 +3016,14 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G69" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
+          <t>9d9513056702d47b1bd0bbeb48d37404a525c1ab7193926f0cf92dea38694c73</t>
         </is>
       </c>
     </row>
@@ -3052,14 +3052,14 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G70" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
+          <t>9d9513056702d47b1bd0bbeb48d37404a525c1ab7193926f0cf92dea38694c73</t>
         </is>
       </c>
     </row>
@@ -3088,14 +3088,14 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G71" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
+          <t>9d9513056702d47b1bd0bbeb48d37404a525c1ab7193926f0cf92dea38694c73</t>
         </is>
       </c>
     </row>
@@ -3124,14 +3124,14 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G72" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
+          <t>9d9513056702d47b1bd0bbeb48d37404a525c1ab7193926f0cf92dea38694c73</t>
         </is>
       </c>
     </row>
@@ -3160,14 +3160,14 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G73" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>85feaa0400960222d96e90e24e2f805283afcb85368cdfe334a245128b10f02e</t>
+          <t>9d9513056702d47b1bd0bbeb48d37404a525c1ab7193926f0cf92dea38694c73</t>
         </is>
       </c>
     </row>
@@ -3196,14 +3196,14 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
+          <t>affe3625fc7982f2e99737a900fe1b637f3d13a90b101c1f95ed0fee2868ce2d</t>
         </is>
       </c>
     </row>
@@ -3232,14 +3232,14 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
+          <t>affe3625fc7982f2e99737a900fe1b637f3d13a90b101c1f95ed0fee2868ce2d</t>
         </is>
       </c>
     </row>
@@ -3268,14 +3268,14 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G76" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
+          <t>affe3625fc7982f2e99737a900fe1b637f3d13a90b101c1f95ed0fee2868ce2d</t>
         </is>
       </c>
     </row>
@@ -3304,14 +3304,14 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
+          <t>affe3625fc7982f2e99737a900fe1b637f3d13a90b101c1f95ed0fee2868ce2d</t>
         </is>
       </c>
     </row>
@@ -3340,14 +3340,14 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G78" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
+          <t>affe3625fc7982f2e99737a900fe1b637f3d13a90b101c1f95ed0fee2868ce2d</t>
         </is>
       </c>
     </row>
@@ -3376,14 +3376,14 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G79" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
+          <t>affe3625fc7982f2e99737a900fe1b637f3d13a90b101c1f95ed0fee2868ce2d</t>
         </is>
       </c>
     </row>
@@ -3412,14 +3412,14 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G80" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
+          <t>affe3625fc7982f2e99737a900fe1b637f3d13a90b101c1f95ed0fee2868ce2d</t>
         </is>
       </c>
     </row>
@@ -3448,14 +3448,14 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>f45ea1cf2f9581fb2fc0aa8d152606d75c85c7e3a96494cd5af8cfe528f58226</t>
+          <t>affe3625fc7982f2e99737a900fe1b637f3d13a90b101c1f95ed0fee2868ce2d</t>
         </is>
       </c>
     </row>
@@ -3484,14 +3484,14 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
+          <t>147afad30a49a8acf0029b549f9a13460c8a63226390ab48d9f5ebf9d82c5350</t>
         </is>
       </c>
     </row>
@@ -3520,14 +3520,14 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
+          <t>147afad30a49a8acf0029b549f9a13460c8a63226390ab48d9f5ebf9d82c5350</t>
         </is>
       </c>
     </row>
@@ -3556,14 +3556,14 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G84" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
+          <t>147afad30a49a8acf0029b549f9a13460c8a63226390ab48d9f5ebf9d82c5350</t>
         </is>
       </c>
     </row>
@@ -3592,14 +3592,14 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G85" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
+          <t>147afad30a49a8acf0029b549f9a13460c8a63226390ab48d9f5ebf9d82c5350</t>
         </is>
       </c>
     </row>
@@ -3628,14 +3628,14 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
+          <t>147afad30a49a8acf0029b549f9a13460c8a63226390ab48d9f5ebf9d82c5350</t>
         </is>
       </c>
     </row>
@@ -3664,14 +3664,14 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G87" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
+          <t>147afad30a49a8acf0029b549f9a13460c8a63226390ab48d9f5ebf9d82c5350</t>
         </is>
       </c>
     </row>
@@ -3700,14 +3700,14 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G88" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
+          <t>147afad30a49a8acf0029b549f9a13460c8a63226390ab48d9f5ebf9d82c5350</t>
         </is>
       </c>
     </row>
@@ -3736,14 +3736,14 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G89" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4c944786ef17ad5e99bc26b371e71c84c340e8fb2b648e0d67cd05989924ba07</t>
+          <t>147afad30a49a8acf0029b549f9a13460c8a63226390ab48d9f5ebf9d82c5350</t>
         </is>
       </c>
     </row>
@@ -3772,14 +3772,14 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
+          <t>0e2b2a6c105d6448361b029377c3becd8d42eae0796d503b00b519aff0d0d459</t>
         </is>
       </c>
     </row>
@@ -3808,14 +3808,14 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G91" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
+          <t>0e2b2a6c105d6448361b029377c3becd8d42eae0796d503b00b519aff0d0d459</t>
         </is>
       </c>
     </row>
@@ -3844,14 +3844,14 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G92" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
+          <t>0e2b2a6c105d6448361b029377c3becd8d42eae0796d503b00b519aff0d0d459</t>
         </is>
       </c>
     </row>
@@ -3880,14 +3880,14 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G93" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
+          <t>0e2b2a6c105d6448361b029377c3becd8d42eae0796d503b00b519aff0d0d459</t>
         </is>
       </c>
     </row>
@@ -3916,14 +3916,14 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
+          <t>0e2b2a6c105d6448361b029377c3becd8d42eae0796d503b00b519aff0d0d459</t>
         </is>
       </c>
     </row>
@@ -3952,14 +3952,14 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G95" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>e2398cbce1596ee34262a8a8632595890627aea1bd4edf80de95a4ceee299876</t>
+          <t>0e2b2a6c105d6448361b029377c3becd8d42eae0796d503b00b519aff0d0d459</t>
         </is>
       </c>
     </row>
@@ -3988,14 +3988,14 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
+          <t>a5ad1fdea407b66304153e1c7e6adbaed86ec96efeafe55087be48c4a71bcee7</t>
         </is>
       </c>
     </row>
@@ -4024,14 +4024,14 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G97" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
+          <t>a5ad1fdea407b66304153e1c7e6adbaed86ec96efeafe55087be48c4a71bcee7</t>
         </is>
       </c>
     </row>
@@ -4060,14 +4060,14 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G98" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
+          <t>a5ad1fdea407b66304153e1c7e6adbaed86ec96efeafe55087be48c4a71bcee7</t>
         </is>
       </c>
     </row>
@@ -4096,14 +4096,14 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
+          <t>a5ad1fdea407b66304153e1c7e6adbaed86ec96efeafe55087be48c4a71bcee7</t>
         </is>
       </c>
     </row>
@@ -4132,14 +4132,14 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G100" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
+          <t>a5ad1fdea407b66304153e1c7e6adbaed86ec96efeafe55087be48c4a71bcee7</t>
         </is>
       </c>
     </row>
@@ -4168,14 +4168,14 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G101" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>b9cc314a5510cd072e0d1b8aa24bd8f236822aa3cf24f80754619b6cc6bb188a</t>
+          <t>a5ad1fdea407b66304153e1c7e6adbaed86ec96efeafe55087be48c4a71bcee7</t>
         </is>
       </c>
     </row>
@@ -4204,14 +4204,14 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
+          <t>b0d3a8a1fccf4c0cd798ab65126384f99d67f709e25c32941a0ad823991f4ac9</t>
         </is>
       </c>
     </row>
@@ -4240,14 +4240,14 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
+          <t>b0d3a8a1fccf4c0cd798ab65126384f99d67f709e25c32941a0ad823991f4ac9</t>
         </is>
       </c>
     </row>
@@ -4276,14 +4276,14 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
+          <t>b0d3a8a1fccf4c0cd798ab65126384f99d67f709e25c32941a0ad823991f4ac9</t>
         </is>
       </c>
     </row>
@@ -4312,14 +4312,14 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
+          <t>b0d3a8a1fccf4c0cd798ab65126384f99d67f709e25c32941a0ad823991f4ac9</t>
         </is>
       </c>
     </row>
@@ -4348,14 +4348,14 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
+          <t>b0d3a8a1fccf4c0cd798ab65126384f99d67f709e25c32941a0ad823991f4ac9</t>
         </is>
       </c>
     </row>
@@ -4384,14 +4384,14 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G107" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>6448349e6a990a714574bdcd80cfff2cab0ac94ab534c2b142190e62fc3f966b</t>
+          <t>b0d3a8a1fccf4c0cd798ab65126384f99d67f709e25c32941a0ad823991f4ac9</t>
         </is>
       </c>
     </row>
@@ -4420,14 +4420,14 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G108" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
+          <t>af24a1b7d114145c13db625a10173a20ee6cfd08492c90dd3f2ffa9d149cffed</t>
         </is>
       </c>
     </row>
@@ -4456,14 +4456,14 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G109" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
+          <t>af24a1b7d114145c13db625a10173a20ee6cfd08492c90dd3f2ffa9d149cffed</t>
         </is>
       </c>
     </row>
@@ -4492,14 +4492,14 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G110" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
+          <t>af24a1b7d114145c13db625a10173a20ee6cfd08492c90dd3f2ffa9d149cffed</t>
         </is>
       </c>
     </row>
@@ -4528,14 +4528,14 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G111" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
+          <t>af24a1b7d114145c13db625a10173a20ee6cfd08492c90dd3f2ffa9d149cffed</t>
         </is>
       </c>
     </row>
@@ -4564,14 +4564,14 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G112" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
+          <t>af24a1b7d114145c13db625a10173a20ee6cfd08492c90dd3f2ffa9d149cffed</t>
         </is>
       </c>
     </row>
@@ -4600,14 +4600,14 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G113" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1ba615cd4e40209584bbd1951e14bd616542fad017318a159ca25900b2686231</t>
+          <t>af24a1b7d114145c13db625a10173a20ee6cfd08492c90dd3f2ffa9d149cffed</t>
         </is>
       </c>
     </row>
@@ -4636,14 +4636,14 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G114" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
+          <t>c0755984386001b413c745cda37c491fa6e88c16646ba9de4596a486d0862dd3</t>
         </is>
       </c>
     </row>
@@ -4672,14 +4672,14 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G115" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
+          <t>c0755984386001b413c745cda37c491fa6e88c16646ba9de4596a486d0862dd3</t>
         </is>
       </c>
     </row>
@@ -4708,14 +4708,14 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G116" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
+          <t>c0755984386001b413c745cda37c491fa6e88c16646ba9de4596a486d0862dd3</t>
         </is>
       </c>
     </row>
@@ -4744,14 +4744,14 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G117" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
+          <t>c0755984386001b413c745cda37c491fa6e88c16646ba9de4596a486d0862dd3</t>
         </is>
       </c>
     </row>
@@ -4780,14 +4780,14 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G118" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
+          <t>c0755984386001b413c745cda37c491fa6e88c16646ba9de4596a486d0862dd3</t>
         </is>
       </c>
     </row>
@@ -4816,14 +4816,14 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G119" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
+          <t>c0755984386001b413c745cda37c491fa6e88c16646ba9de4596a486d0862dd3</t>
         </is>
       </c>
     </row>
@@ -4852,14 +4852,14 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G120" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
+          <t>c0755984386001b413c745cda37c491fa6e88c16646ba9de4596a486d0862dd3</t>
         </is>
       </c>
     </row>
@@ -4888,14 +4888,14 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G121" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>5d28c7da1d7cbf4e051167e130b73083e880801cd4e1b9127dce5ff4513359f6</t>
+          <t>c0755984386001b413c745cda37c491fa6e88c16646ba9de4596a486d0862dd3</t>
         </is>
       </c>
     </row>
@@ -4924,14 +4924,14 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G122" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
+          <t>232cdf72114fbbf318e6f7d971bbe72638988f25dbf8d56959adc461a32addf5</t>
         </is>
       </c>
     </row>
@@ -4960,14 +4960,14 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G123" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
+          <t>232cdf72114fbbf318e6f7d971bbe72638988f25dbf8d56959adc461a32addf5</t>
         </is>
       </c>
     </row>
@@ -4996,14 +4996,14 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G124" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
+          <t>232cdf72114fbbf318e6f7d971bbe72638988f25dbf8d56959adc461a32addf5</t>
         </is>
       </c>
     </row>
@@ -5032,14 +5032,14 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G125" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
+          <t>232cdf72114fbbf318e6f7d971bbe72638988f25dbf8d56959adc461a32addf5</t>
         </is>
       </c>
     </row>
@@ -5068,14 +5068,14 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G126" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
+          <t>232cdf72114fbbf318e6f7d971bbe72638988f25dbf8d56959adc461a32addf5</t>
         </is>
       </c>
     </row>
@@ -5104,14 +5104,14 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G127" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
+          <t>232cdf72114fbbf318e6f7d971bbe72638988f25dbf8d56959adc461a32addf5</t>
         </is>
       </c>
     </row>
@@ -5140,14 +5140,14 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G128" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
+          <t>232cdf72114fbbf318e6f7d971bbe72638988f25dbf8d56959adc461a32addf5</t>
         </is>
       </c>
     </row>
@@ -5176,14 +5176,14 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G129" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>450336e0aeb9097e7bd1b1882c084471b5f89d9fbb10d1f36fd2f1fa61dab384</t>
+          <t>232cdf72114fbbf318e6f7d971bbe72638988f25dbf8d56959adc461a32addf5</t>
         </is>
       </c>
     </row>
@@ -5212,14 +5212,14 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
+          <t>23f017dfc72ca4749cc31917d2a69b85021cb7699e7a0588d87814aaeacb8566</t>
         </is>
       </c>
     </row>
@@ -5248,14 +5248,14 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
+          <t>23f017dfc72ca4749cc31917d2a69b85021cb7699e7a0588d87814aaeacb8566</t>
         </is>
       </c>
     </row>
@@ -5284,14 +5284,14 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
+          <t>23f017dfc72ca4749cc31917d2a69b85021cb7699e7a0588d87814aaeacb8566</t>
         </is>
       </c>
     </row>
@@ -5320,14 +5320,14 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G133" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
+          <t>23f017dfc72ca4749cc31917d2a69b85021cb7699e7a0588d87814aaeacb8566</t>
         </is>
       </c>
     </row>
@@ -5356,14 +5356,14 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G134" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
+          <t>23f017dfc72ca4749cc31917d2a69b85021cb7699e7a0588d87814aaeacb8566</t>
         </is>
       </c>
     </row>
@@ -5392,14 +5392,14 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G135" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
+          <t>23f017dfc72ca4749cc31917d2a69b85021cb7699e7a0588d87814aaeacb8566</t>
         </is>
       </c>
     </row>
@@ -5428,14 +5428,14 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G136" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
+          <t>23f017dfc72ca4749cc31917d2a69b85021cb7699e7a0588d87814aaeacb8566</t>
         </is>
       </c>
     </row>
@@ -5464,14 +5464,14 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>3192b55a90eb1a286d8ce59d1bbeaa55307d990a975c049ef636829a3ab564d5</t>
+          <t>23f017dfc72ca4749cc31917d2a69b85021cb7699e7a0588d87814aaeacb8566</t>
         </is>
       </c>
     </row>
@@ -5500,14 +5500,14 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G138" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
+          <t>d89ecc4dddedc61cfddc7c130e4fa257b832ed718b3352fca9a1fefd9ae408e9</t>
         </is>
       </c>
     </row>
@@ -5536,14 +5536,14 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G139" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
+          <t>d89ecc4dddedc61cfddc7c130e4fa257b832ed718b3352fca9a1fefd9ae408e9</t>
         </is>
       </c>
     </row>
@@ -5572,14 +5572,14 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
+          <t>d89ecc4dddedc61cfddc7c130e4fa257b832ed718b3352fca9a1fefd9ae408e9</t>
         </is>
       </c>
     </row>
@@ -5608,14 +5608,14 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G141" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
+          <t>d89ecc4dddedc61cfddc7c130e4fa257b832ed718b3352fca9a1fefd9ae408e9</t>
         </is>
       </c>
     </row>
@@ -5644,14 +5644,14 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G142" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
+          <t>d89ecc4dddedc61cfddc7c130e4fa257b832ed718b3352fca9a1fefd9ae408e9</t>
         </is>
       </c>
     </row>
@@ -5680,14 +5680,14 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G143" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
+          <t>d89ecc4dddedc61cfddc7c130e4fa257b832ed718b3352fca9a1fefd9ae408e9</t>
         </is>
       </c>
     </row>
@@ -5716,14 +5716,14 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G144" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
+          <t>d89ecc4dddedc61cfddc7c130e4fa257b832ed718b3352fca9a1fefd9ae408e9</t>
         </is>
       </c>
     </row>
@@ -5752,14 +5752,14 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G145" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>86de95a85e737cf0aeae4ddb5445cfd2b6f09d91a65c127ba7ffcdd19166bfd5</t>
+          <t>d89ecc4dddedc61cfddc7c130e4fa257b832ed718b3352fca9a1fefd9ae408e9</t>
         </is>
       </c>
     </row>
@@ -5788,14 +5788,14 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G146" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
+          <t>1129f2e2cf17f30782017ce3c5929384e16cf744e5f7bcd3003e2e3de7aecf4d</t>
         </is>
       </c>
     </row>
@@ -5824,14 +5824,14 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G147" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
+          <t>1129f2e2cf17f30782017ce3c5929384e16cf744e5f7bcd3003e2e3de7aecf4d</t>
         </is>
       </c>
     </row>
@@ -5860,14 +5860,14 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G148" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
+          <t>1129f2e2cf17f30782017ce3c5929384e16cf744e5f7bcd3003e2e3de7aecf4d</t>
         </is>
       </c>
     </row>
@@ -5896,14 +5896,14 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G149" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
+          <t>1129f2e2cf17f30782017ce3c5929384e16cf744e5f7bcd3003e2e3de7aecf4d</t>
         </is>
       </c>
     </row>
@@ -5932,14 +5932,14 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G150" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
+          <t>1129f2e2cf17f30782017ce3c5929384e16cf744e5f7bcd3003e2e3de7aecf4d</t>
         </is>
       </c>
     </row>
@@ -5968,14 +5968,14 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G151" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>580a76eeaa6f8d86c8abb18e563638212a6c296f749707b7c8ccc28afd7a5af3</t>
+          <t>1129f2e2cf17f30782017ce3c5929384e16cf744e5f7bcd3003e2e3de7aecf4d</t>
         </is>
       </c>
     </row>
@@ -6004,14 +6004,14 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G152" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
+          <t>55c1db9ec056dbedf9c2d123f35c6d5fbbaa4bbc2fb416d87e17c7b5749a9a71</t>
         </is>
       </c>
     </row>
@@ -6040,14 +6040,14 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G153" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
+          <t>55c1db9ec056dbedf9c2d123f35c6d5fbbaa4bbc2fb416d87e17c7b5749a9a71</t>
         </is>
       </c>
     </row>
@@ -6076,14 +6076,14 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G154" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
+          <t>55c1db9ec056dbedf9c2d123f35c6d5fbbaa4bbc2fb416d87e17c7b5749a9a71</t>
         </is>
       </c>
     </row>
@@ -6112,14 +6112,14 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G155" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
+          <t>55c1db9ec056dbedf9c2d123f35c6d5fbbaa4bbc2fb416d87e17c7b5749a9a71</t>
         </is>
       </c>
     </row>
@@ -6148,14 +6148,14 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G156" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
+          <t>55c1db9ec056dbedf9c2d123f35c6d5fbbaa4bbc2fb416d87e17c7b5749a9a71</t>
         </is>
       </c>
     </row>
@@ -6184,14 +6184,14 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G157" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>0689ef590a22fd9d307e40e4bc901d6771ec7245813b0d872a220884d5a1613c</t>
+          <t>55c1db9ec056dbedf9c2d123f35c6d5fbbaa4bbc2fb416d87e17c7b5749a9a71</t>
         </is>
       </c>
     </row>
@@ -6220,14 +6220,14 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G158" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
+          <t>df4f6a2f83977d5a4ff6ea265d610e11996bc2c9bf9060b6e4ffbe9717419830</t>
         </is>
       </c>
     </row>
@@ -6256,14 +6256,14 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G159" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
+          <t>df4f6a2f83977d5a4ff6ea265d610e11996bc2c9bf9060b6e4ffbe9717419830</t>
         </is>
       </c>
     </row>
@@ -6292,14 +6292,14 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G160" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
+          <t>df4f6a2f83977d5a4ff6ea265d610e11996bc2c9bf9060b6e4ffbe9717419830</t>
         </is>
       </c>
     </row>
@@ -6328,14 +6328,14 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G161" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
+          <t>df4f6a2f83977d5a4ff6ea265d610e11996bc2c9bf9060b6e4ffbe9717419830</t>
         </is>
       </c>
     </row>
@@ -6364,14 +6364,14 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G162" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
+          <t>df4f6a2f83977d5a4ff6ea265d610e11996bc2c9bf9060b6e4ffbe9717419830</t>
         </is>
       </c>
     </row>
@@ -6400,14 +6400,14 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G163" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>e26f4f8a7af4cf9634c4bd5e3595676f9093747be7eb3d461cfb4ac809960969</t>
+          <t>df4f6a2f83977d5a4ff6ea265d610e11996bc2c9bf9060b6e4ffbe9717419830</t>
         </is>
       </c>
     </row>
@@ -6436,14 +6436,14 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G164" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
+          <t>645ea67b6c1b063dc79eabf39a40132a82001895386612c33d210c42af669cc8</t>
         </is>
       </c>
     </row>
@@ -6472,14 +6472,14 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G165" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
+          <t>645ea67b6c1b063dc79eabf39a40132a82001895386612c33d210c42af669cc8</t>
         </is>
       </c>
     </row>
@@ -6508,14 +6508,14 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G166" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
+          <t>645ea67b6c1b063dc79eabf39a40132a82001895386612c33d210c42af669cc8</t>
         </is>
       </c>
     </row>
@@ -6544,14 +6544,14 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G167" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
+          <t>645ea67b6c1b063dc79eabf39a40132a82001895386612c33d210c42af669cc8</t>
         </is>
       </c>
     </row>
@@ -6580,14 +6580,14 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G168" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
+          <t>645ea67b6c1b063dc79eabf39a40132a82001895386612c33d210c42af669cc8</t>
         </is>
       </c>
     </row>
@@ -6616,14 +6616,14 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G169" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>0b0b61511920c448778821146dafb8e19504128b4786359b6a76b0f75ddf928a</t>
+          <t>645ea67b6c1b063dc79eabf39a40132a82001895386612c33d210c42af669cc8</t>
         </is>
       </c>
     </row>
@@ -6652,14 +6652,14 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G170" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
+          <t>52f2e37313ec9c157c0804013cb0271eba7a5ddd4cb6c4267102eb7faede102f</t>
         </is>
       </c>
     </row>
@@ -6688,14 +6688,14 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G171" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
+          <t>52f2e37313ec9c157c0804013cb0271eba7a5ddd4cb6c4267102eb7faede102f</t>
         </is>
       </c>
     </row>
@@ -6724,14 +6724,14 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G172" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
+          <t>52f2e37313ec9c157c0804013cb0271eba7a5ddd4cb6c4267102eb7faede102f</t>
         </is>
       </c>
     </row>
@@ -6760,14 +6760,14 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G173" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
+          <t>52f2e37313ec9c157c0804013cb0271eba7a5ddd4cb6c4267102eb7faede102f</t>
         </is>
       </c>
     </row>
@@ -6796,14 +6796,14 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G174" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
+          <t>52f2e37313ec9c157c0804013cb0271eba7a5ddd4cb6c4267102eb7faede102f</t>
         </is>
       </c>
     </row>
@@ -6832,14 +6832,14 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G175" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
+          <t>52f2e37313ec9c157c0804013cb0271eba7a5ddd4cb6c4267102eb7faede102f</t>
         </is>
       </c>
     </row>
@@ -6868,14 +6868,14 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G176" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
+          <t>52f2e37313ec9c157c0804013cb0271eba7a5ddd4cb6c4267102eb7faede102f</t>
         </is>
       </c>
     </row>
@@ -6904,14 +6904,14 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>5006</v>
+        <v>5903</v>
       </c>
       <c r="G177" t="n">
-        <v>0.4671955202986467</v>
+        <v>0.4736039794608473</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>5fabaf4682ab23855dc54ad7b031770cef720612f88f1e337638c289aee2604a</t>
+          <t>52f2e37313ec9c157c0804013cb0271eba7a5ddd4cb6c4267102eb7faede102f</t>
         </is>
       </c>
     </row>
@@ -6940,14 +6940,14 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G178" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
+          <t>1041fdaf26011e4514bedfdf148ea83b885b926db8c495ef6d76bab237130ce7</t>
         </is>
       </c>
     </row>
@@ -6976,14 +6976,14 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G179" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
+          <t>1041fdaf26011e4514bedfdf148ea83b885b926db8c495ef6d76bab237130ce7</t>
         </is>
       </c>
     </row>
@@ -7012,14 +7012,14 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G180" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
+          <t>1041fdaf26011e4514bedfdf148ea83b885b926db8c495ef6d76bab237130ce7</t>
         </is>
       </c>
     </row>
@@ -7048,14 +7048,14 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G181" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
+          <t>1041fdaf26011e4514bedfdf148ea83b885b926db8c495ef6d76bab237130ce7</t>
         </is>
       </c>
     </row>
@@ -7084,14 +7084,14 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G182" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
+          <t>1041fdaf26011e4514bedfdf148ea83b885b926db8c495ef6d76bab237130ce7</t>
         </is>
       </c>
     </row>
@@ -7120,14 +7120,14 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G183" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
+          <t>1041fdaf26011e4514bedfdf148ea83b885b926db8c495ef6d76bab237130ce7</t>
         </is>
       </c>
     </row>
@@ -7156,14 +7156,14 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G184" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
+          <t>1041fdaf26011e4514bedfdf148ea83b885b926db8c495ef6d76bab237130ce7</t>
         </is>
       </c>
     </row>
@@ -7192,14 +7192,14 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3298</v>
+        <v>4279</v>
       </c>
       <c r="G185" t="n">
-        <v>0.49150521609538</v>
+        <v>0.4704265611257696</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>748d964710788bf19a41e3a2c3e06d4cb30a75bed7e2ae1c86b6730107b9ee80</t>
+          <t>1041fdaf26011e4514bedfdf148ea83b885b926db8c495ef6d76bab237130ce7</t>
         </is>
       </c>
     </row>
@@ -7228,14 +7228,14 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G186" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
+          <t>6953dcc3c8b84c8954b12b44f7cdc224ce9cedf029475014442f08412b2619dc</t>
         </is>
       </c>
     </row>
@@ -7264,14 +7264,14 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G187" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
+          <t>6953dcc3c8b84c8954b12b44f7cdc224ce9cedf029475014442f08412b2619dc</t>
         </is>
       </c>
     </row>
@@ -7300,14 +7300,14 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G188" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
+          <t>6953dcc3c8b84c8954b12b44f7cdc224ce9cedf029475014442f08412b2619dc</t>
         </is>
       </c>
     </row>
@@ -7336,14 +7336,14 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G189" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
+          <t>6953dcc3c8b84c8954b12b44f7cdc224ce9cedf029475014442f08412b2619dc</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7372,14 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G190" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
+          <t>6953dcc3c8b84c8954b12b44f7cdc224ce9cedf029475014442f08412b2619dc</t>
         </is>
       </c>
     </row>
@@ -7408,14 +7408,14 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G191" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
+          <t>6953dcc3c8b84c8954b12b44f7cdc224ce9cedf029475014442f08412b2619dc</t>
         </is>
       </c>
     </row>
@@ -7444,14 +7444,14 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G192" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
+          <t>6953dcc3c8b84c8954b12b44f7cdc224ce9cedf029475014442f08412b2619dc</t>
         </is>
       </c>
     </row>
@@ -7480,14 +7480,14 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>4061</v>
+        <v>2382</v>
       </c>
       <c r="G193" t="n">
-        <v>0.4777647058823529</v>
+        <v>0.4913366336633663</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>777acd41c0f3b8bb891d6d62f1dd89886cc4b0eda9d7ffa70f0281652c8fdfb9</t>
+          <t>6953dcc3c8b84c8954b12b44f7cdc224ce9cedf029475014442f08412b2619dc</t>
         </is>
       </c>
     </row>
@@ -7516,14 +7516,14 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G194" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
+          <t>299b4a414b2eab9401c651201dccc265fffaf9bdbd97306441d5d276250e5645</t>
         </is>
       </c>
     </row>
@@ -7552,14 +7552,14 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G195" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
+          <t>299b4a414b2eab9401c651201dccc265fffaf9bdbd97306441d5d276250e5645</t>
         </is>
       </c>
     </row>
@@ -7588,14 +7588,14 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G196" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
+          <t>299b4a414b2eab9401c651201dccc265fffaf9bdbd97306441d5d276250e5645</t>
         </is>
       </c>
     </row>
@@ -7624,14 +7624,14 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G197" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
+          <t>299b4a414b2eab9401c651201dccc265fffaf9bdbd97306441d5d276250e5645</t>
         </is>
       </c>
     </row>
@@ -7660,14 +7660,14 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G198" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
+          <t>299b4a414b2eab9401c651201dccc265fffaf9bdbd97306441d5d276250e5645</t>
         </is>
       </c>
     </row>
@@ -7696,14 +7696,14 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G199" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
+          <t>299b4a414b2eab9401c651201dccc265fffaf9bdbd97306441d5d276250e5645</t>
         </is>
       </c>
     </row>
@@ -7732,14 +7732,14 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G200" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
+          <t>299b4a414b2eab9401c651201dccc265fffaf9bdbd97306441d5d276250e5645</t>
         </is>
       </c>
     </row>
@@ -7768,14 +7768,14 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3844</v>
+        <v>3645</v>
       </c>
       <c r="G201" t="n">
-        <v>0.4827326384528444</v>
+        <v>0.4872994652406417</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>c7f0026d7161f223cb4251c37c0b633c691439fcc7903d5134780036ed7a7450</t>
+          <t>299b4a414b2eab9401c651201dccc265fffaf9bdbd97306441d5d276250e5645</t>
         </is>
       </c>
     </row>
@@ -7804,14 +7804,14 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G202" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
+          <t>62da4ffa6976a08578f02825fe9e637fae16e2d1bc8acb7dc2f44f56a4a8183c</t>
         </is>
       </c>
     </row>
@@ -7840,14 +7840,14 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G203" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
+          <t>62da4ffa6976a08578f02825fe9e637fae16e2d1bc8acb7dc2f44f56a4a8183c</t>
         </is>
       </c>
     </row>
@@ -7876,14 +7876,14 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G204" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
+          <t>62da4ffa6976a08578f02825fe9e637fae16e2d1bc8acb7dc2f44f56a4a8183c</t>
         </is>
       </c>
     </row>
@@ -7912,14 +7912,14 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G205" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
+          <t>62da4ffa6976a08578f02825fe9e637fae16e2d1bc8acb7dc2f44f56a4a8183c</t>
         </is>
       </c>
     </row>
@@ -7948,14 +7948,14 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G206" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
+          <t>62da4ffa6976a08578f02825fe9e637fae16e2d1bc8acb7dc2f44f56a4a8183c</t>
         </is>
       </c>
     </row>
@@ -7984,14 +7984,14 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>3336</v>
+        <v>4291</v>
       </c>
       <c r="G207" t="n">
-        <v>0.4562363238512035</v>
+        <v>0.4590286692340608</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2379e35e5b6119ce377c24fd8ed49d3a74f0f4c179a5a0873effd896cc0d5021</t>
+          <t>62da4ffa6976a08578f02825fe9e637fae16e2d1bc8acb7dc2f44f56a4a8183c</t>
         </is>
       </c>
     </row>
@@ -8020,14 +8020,14 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G208" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
+          <t>86f367e72396b85c07d766e3d8897bb699519abae3a99f85e33cc7dfeea610bc</t>
         </is>
       </c>
     </row>
@@ -8056,14 +8056,14 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G209" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
+          <t>86f367e72396b85c07d766e3d8897bb699519abae3a99f85e33cc7dfeea610bc</t>
         </is>
       </c>
     </row>
@@ -8092,14 +8092,14 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G210" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
+          <t>86f367e72396b85c07d766e3d8897bb699519abae3a99f85e33cc7dfeea610bc</t>
         </is>
       </c>
     </row>
@@ -8128,14 +8128,14 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G211" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
+          <t>86f367e72396b85c07d766e3d8897bb699519abae3a99f85e33cc7dfeea610bc</t>
         </is>
       </c>
     </row>
@@ -8164,14 +8164,14 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G212" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
+          <t>86f367e72396b85c07d766e3d8897bb699519abae3a99f85e33cc7dfeea610bc</t>
         </is>
       </c>
     </row>
@@ -8200,14 +8200,14 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="G213" t="n">
-        <v>0.4343419925777905</v>
+        <v>0.4519202579888596</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>274ca9feec959c561305c4b83dca093cd8c48ef9858d459342e424ceefbebd50</t>
+          <t>86f367e72396b85c07d766e3d8897bb699519abae3a99f85e33cc7dfeea610bc</t>
         </is>
       </c>
     </row>
@@ -8236,14 +8236,14 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G214" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
+          <t>128bf5c92302f033b8b906b75e2ea40c5e66778651d712dd7f93cafe2252d176</t>
         </is>
       </c>
     </row>
@@ -8272,14 +8272,14 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G215" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
+          <t>128bf5c92302f033b8b906b75e2ea40c5e66778651d712dd7f93cafe2252d176</t>
         </is>
       </c>
     </row>
@@ -8308,14 +8308,14 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G216" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
+          <t>128bf5c92302f033b8b906b75e2ea40c5e66778651d712dd7f93cafe2252d176</t>
         </is>
       </c>
     </row>
@@ -8344,14 +8344,14 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G217" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
+          <t>128bf5c92302f033b8b906b75e2ea40c5e66778651d712dd7f93cafe2252d176</t>
         </is>
       </c>
     </row>
@@ -8380,14 +8380,14 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G218" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
+          <t>128bf5c92302f033b8b906b75e2ea40c5e66778651d712dd7f93cafe2252d176</t>
         </is>
       </c>
     </row>
@@ -8416,14 +8416,14 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>2344</v>
+        <v>1439</v>
       </c>
       <c r="G219" t="n">
-        <v>0.3942809083263246</v>
+        <v>0.3957645764576458</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>43e0133e5bed8a3db42f88e0c0a7d3566d04fcb3ee4ad58712f5460d85c00168</t>
+          <t>128bf5c92302f033b8b906b75e2ea40c5e66778651d712dd7f93cafe2252d176</t>
         </is>
       </c>
     </row>
@@ -8452,14 +8452,14 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G220" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
+          <t>16258816e7370808523fce10662c6235711e6e97842be3ad38cabd3cd557470b</t>
         </is>
       </c>
     </row>
@@ -8488,14 +8488,14 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G221" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
+          <t>16258816e7370808523fce10662c6235711e6e97842be3ad38cabd3cd557470b</t>
         </is>
       </c>
     </row>
@@ -8524,14 +8524,14 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G222" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
+          <t>16258816e7370808523fce10662c6235711e6e97842be3ad38cabd3cd557470b</t>
         </is>
       </c>
     </row>
@@ -8560,14 +8560,14 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G223" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
+          <t>16258816e7370808523fce10662c6235711e6e97842be3ad38cabd3cd557470b</t>
         </is>
       </c>
     </row>
@@ -8596,14 +8596,14 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G224" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
+          <t>16258816e7370808523fce10662c6235711e6e97842be3ad38cabd3cd557470b</t>
         </is>
       </c>
     </row>
@@ -8632,14 +8632,14 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2305</v>
+        <v>2215</v>
       </c>
       <c r="G225" t="n">
-        <v>0.4473122452940035</v>
+        <v>0.3948306595365419</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>e452726b4b98ef86150ce8ea8b1964ff56e38f74aa112639fe74f3cb1e76e45b</t>
+          <t>16258816e7370808523fce10662c6235711e6e97842be3ad38cabd3cd557470b</t>
         </is>
       </c>
     </row>
